--- a/comparison_mapa.xlsx
+++ b/comparison_mapa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\home\mudathir\all\sls-reachability\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1C7F102-EC07-4EB7-B1E8-2EF7A410B432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{222526C8-91E2-4C1F-8B8A-D0A59470C17E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6D35E12D-3E59-4DB7-960F-6311366F8180}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{6D35E12D-3E59-4DB7-960F-6311366F8180}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet3" sheetId="4" r:id="rId1"/>
@@ -19,14 +19,14 @@
     <sheet name="comparison_mapa" sheetId="1" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlcn.WorksheetConnection_comparison_mapa.xlsxTable11" hidden="1">Table1[]</definedName>
-    <definedName name="_xlcn.WorksheetConnection_comparison_mapaA1I2411" hidden="1">comparison_mapa!$A$1:$I$241</definedName>
+    <definedName name="_xlcn.WorksheetConnection_comparison_mapa.xlsxTable1" hidden="1">Table1[]</definedName>
+    <definedName name="_xlcn.WorksheetConnection_comparison_mapaA1I241" hidden="1">comparison_mapa!$A$1:$I$241</definedName>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Sheet3!$A$3:$L$9</definedName>
   </definedNames>
   <calcPr calcId="0"/>
   <pivotCaches>
-    <pivotCache cacheId="30" r:id="rId5"/>
-    <pivotCache cacheId="62" r:id="rId6"/>
+    <pivotCache cacheId="0" r:id="rId5"/>
+    <pivotCache cacheId="1" r:id="rId6"/>
   </pivotCaches>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{FCE2AD5D-F65C-4FA6-A056-5C36A1767C68}">
@@ -64,7 +64,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Range" autoDelete="1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_comparison_mapaA1I2411"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_comparison_mapaA1I241"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -73,7 +73,7 @@
     <extLst>
       <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{DE250136-89BD-433C-8126-D09CA5730AF9}">
         <x15:connection id="Table1">
-          <x15:rangePr sourceName="_xlcn.WorksheetConnection_comparison_mapa.xlsxTable11"/>
+          <x15:rangePr sourceName="_xlcn.WorksheetConnection_comparison_mapa.xlsxTable1"/>
         </x15:connection>
       </ext>
     </extLst>
@@ -2872,16 +2872,15 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" pivotButton="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="10" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
@@ -2929,48 +2928,6 @@
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
   <dxfs count="15">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="0"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4"/>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -3323,6 +3280,48 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4"/>
+          <bgColor theme="4"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -6139,7 +6138,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2282AA53-B473-43DB-BA1B-E3BF5F531AFC}" name="PivotTable5" cacheId="62" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 without model" colHeaderCaption="cvc5 with model">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{2282AA53-B473-43DB-BA1B-E3BF5F531AFC}" name="PivotTable5" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 without model" colHeaderCaption="cvc5 with model">
   <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="3">
     <pivotField axis="axisCol" allDrilled="1" subtotalTop="0" showAll="0" dataSourceSort="1" defaultSubtotal="0" defaultAttributeDrillState="1">
@@ -6249,161 +6248,7 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable2.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E29FAC8A-5B65-4AF0-A8D9-ABA032F59E85}" name="PivotTable2" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
-  <location ref="A34:E39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD4AD958-16D5-43AB-9783-D8FF1F67C0E9}" name="PivotTable1" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
-  <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
-  <pivotFields count="9">
-    <pivotField showAll="0"/>
-    <pivotField axis="axisRow" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField dataField="1" showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField axis="axisCol" showAll="0">
-      <items count="4">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
-        <item t="default"/>
-      </items>
-    </pivotField>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-    <pivotField showAll="0"/>
-  </pivotFields>
-  <rowFields count="1">
-    <field x="1"/>
-  </rowFields>
-  <rowItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </rowItems>
-  <colFields count="1">
-    <field x="4"/>
-  </colFields>
-  <colItems count="4">
-    <i>
-      <x/>
-    </i>
-    <i>
-      <x v="1"/>
-    </i>
-    <i>
-      <x v="2"/>
-    </i>
-    <i t="grand">
-      <x/>
-    </i>
-  </colItems>
-  <dataFields count="1">
-    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
-  </dataFields>
-  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
-      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
-    </ext>
-    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
-      <xpdl:pivotTableDefinition16/>
-    </ext>
-  </extLst>
-</pivotTableDefinition>
-</file>
-
-<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9FCE0216-C01D-470F-B4C3-6DDA14299962}" name="PivotTable4" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 bags results">
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{9FCE0216-C01D-470F-B4C3-6DDA14299962}" name="PivotTable4" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 bags results">
   <location ref="A14:E19" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -6480,8 +6325,8 @@
 </pivotTableDefinition>
 </file>
 
-<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8BD9776-8DB4-414B-9C9A-27AC290A8751}" name="PivotTable3" cacheId="30" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 bags results" colHeaderCaption="cvc5 lia results">
+<file path=xl/pivotTables/pivotTable3.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{D8BD9776-8DB4-414B-9C9A-27AC290A8751}" name="PivotTable3" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="cvc5 bags results" colHeaderCaption="cvc5 lia results">
   <location ref="A24:E29" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
   <pivotFields count="9">
     <pivotField showAll="0"/>
@@ -6521,6 +6366,160 @@
     </i>
     <i>
       <x v="3"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable4.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{E29FAC8A-5B65-4AF0-A8D9-ABA032F59E85}" name="PivotTable2" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
+  <location ref="A34:E39" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </rowItems>
+  <colFields count="1">
+    <field x="4"/>
+  </colFields>
+  <colItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
+    </i>
+    <i t="grand">
+      <x/>
+    </i>
+  </colItems>
+  <dataFields count="1">
+    <dataField name="Count of sls duration" fld="2" subtotal="count" baseField="1" baseItem="0"/>
+  </dataFields>
+  <pivotTableStyleInfo name="PivotStyleLight16" showRowHeaders="1" showColHeaders="1" showRowStripes="0" showColStripes="0" showLastColumn="1"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{962EF5D1-5CA2-4c93-8EF4-DBF5C05439D2}">
+      <x14:pivotTableDefinition xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" hideValuesRow="1"/>
+    </ext>
+    <ext xmlns:xpdl="http://schemas.microsoft.com/office/spreadsheetml/2016/pivotdefaultlayout" uri="{747A6164-185A-40DC-8AA5-F01512510D54}">
+      <xpdl:pivotTableDefinition16/>
+    </ext>
+  </extLst>
+</pivotTableDefinition>
+</file>
+
+<file path=xl/pivotTables/pivotTable5.xml><?xml version="1.0" encoding="utf-8"?>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{FD4AD958-16D5-43AB-9783-D8FF1F67C0E9}" name="PivotTable1" cacheId="0" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" itemPrintTitles="1" createdVersion="8" indent="0" outline="1" outlineData="1" multipleFieldFilters="0" rowHeaderCaption="sls results" colHeaderCaption="cvc5 lia results">
+  <location ref="A3:E8" firstHeaderRow="1" firstDataRow="2" firstDataCol="1"/>
+  <pivotFields count="9">
+    <pivotField showAll="0"/>
+    <pivotField axis="axisRow" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField dataField="1" showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField axis="axisCol" showAll="0">
+      <items count="4">
+        <item x="0"/>
+        <item x="1"/>
+        <item x="2"/>
+        <item t="default"/>
+      </items>
+    </pivotField>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+    <pivotField showAll="0"/>
+  </pivotFields>
+  <rowFields count="1">
+    <field x="1"/>
+  </rowFields>
+  <rowItems count="4">
+    <i>
+      <x/>
+    </i>
+    <i>
+      <x v="1"/>
+    </i>
+    <i>
+      <x v="2"/>
     </i>
     <i t="grand">
       <x/>
@@ -6606,21 +6605,21 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B9BD11C-E214-455F-A844-0E067FACF962}" name="Table1" displayName="Table1" ref="A1:L241" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1" tableBorderDxfId="14">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1B9BD11C-E214-455F-A844-0E067FACF962}" name="Table1" displayName="Table1" ref="A1:L241" totalsRowShown="0" headerRowDxfId="14" dataDxfId="13" tableBorderDxfId="12">
   <autoFilter ref="A1:L241" xr:uid="{1B9BD11C-E214-455F-A844-0E067FACF962}"/>
   <tableColumns count="12">
-    <tableColumn id="1" xr3:uid="{A35EB4F4-D359-48A6-8C24-DE457C03B543}" name="sls filename" dataDxfId="13"/>
-    <tableColumn id="2" xr3:uid="{9D27B742-E920-4663-9DEC-9E29E158FAC0}" name="sls result" dataDxfId="12"/>
-    <tableColumn id="3" xr3:uid="{4D595A3C-E1D9-4112-A8C8-19C25E0D5DD7}" name="sls duration" dataDxfId="11"/>
-    <tableColumn id="4" xr3:uid="{856C087F-D7A2-464F-9152-0B5FE897310D}" name="cvc5 lia filename" dataDxfId="10"/>
-    <tableColumn id="5" xr3:uid="{C367E1E9-2AB4-4760-A43B-03B77D90FFDC}" name="cvc5 lia result" dataDxfId="9"/>
-    <tableColumn id="6" xr3:uid="{BB5969BD-AC87-46F3-BAB0-C2C1E6448B11}" name="cvc5 lia duration" dataDxfId="8"/>
-    <tableColumn id="7" xr3:uid="{DF3FC216-EB4C-43D9-8AA2-87DE34DAD973}" name="cvc5 bags filename" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{4F9B66E5-8E85-4361-ABA5-BC2F29A771D5}" name="cvc5 bags result" dataDxfId="6"/>
-    <tableColumn id="9" xr3:uid="{A8A1F1CF-AB11-4112-A4F8-D23CFC8ACD6F}" name="duration" dataDxfId="5"/>
-    <tableColumn id="10" xr3:uid="{012183D6-2AC7-43F9-B765-0F50790F6834}" name="no model filename" dataDxfId="4"/>
-    <tableColumn id="11" xr3:uid="{CA257F87-4563-4FF2-8CC3-68146E18D194}" name="no model result" dataDxfId="3"/>
-    <tableColumn id="12" xr3:uid="{015184C8-CC54-4513-AB91-B0F37F19A315}" name="no model duration" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{A35EB4F4-D359-48A6-8C24-DE457C03B543}" name="sls filename" dataDxfId="11"/>
+    <tableColumn id="2" xr3:uid="{9D27B742-E920-4663-9DEC-9E29E158FAC0}" name="sls result" dataDxfId="10"/>
+    <tableColumn id="3" xr3:uid="{4D595A3C-E1D9-4112-A8C8-19C25E0D5DD7}" name="sls duration" dataDxfId="9"/>
+    <tableColumn id="4" xr3:uid="{856C087F-D7A2-464F-9152-0B5FE897310D}" name="cvc5 lia filename" dataDxfId="8"/>
+    <tableColumn id="5" xr3:uid="{C367E1E9-2AB4-4760-A43B-03B77D90FFDC}" name="cvc5 lia result" dataDxfId="7"/>
+    <tableColumn id="6" xr3:uid="{BB5969BD-AC87-46F3-BAB0-C2C1E6448B11}" name="cvc5 lia duration" dataDxfId="6"/>
+    <tableColumn id="7" xr3:uid="{DF3FC216-EB4C-43D9-8AA2-87DE34DAD973}" name="cvc5 bags filename" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4F9B66E5-8E85-4361-ABA5-BC2F29A771D5}" name="cvc5 bags result" dataDxfId="4"/>
+    <tableColumn id="9" xr3:uid="{A8A1F1CF-AB11-4112-A4F8-D23CFC8ACD6F}" name="duration" dataDxfId="3"/>
+    <tableColumn id="10" xr3:uid="{012183D6-2AC7-43F9-B765-0F50790F6834}" name="no model filename" dataDxfId="2"/>
+    <tableColumn id="11" xr3:uid="{CA257F87-4563-4FF2-8CC3-68146E18D194}" name="no model result" dataDxfId="1"/>
+    <tableColumn id="12" xr3:uid="{015184C8-CC54-4513-AB91-B0F37F19A315}" name="no model duration" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -6961,7 +6960,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
         <v>761</v>
       </c>
     </row>
@@ -7289,12 +7288,10 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>131</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>131</v>
       </c>
     </row>
@@ -7302,14 +7299,13 @@
       <c r="A6" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B6" s="4">
+      <c r="B6">
         <v>6</v>
       </c>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>14</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>20</v>
       </c>
     </row>
@@ -7317,12 +7313,10 @@
       <c r="A7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B7" s="4"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>89</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
         <v>89</v>
       </c>
     </row>
@@ -7330,16 +7324,16 @@
       <c r="A8" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>137</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>14</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>89</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8">
         <v>240</v>
       </c>
     </row>
@@ -7866,14 +7860,13 @@
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="4">
+      <c r="B5">
         <v>114</v>
       </c>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="4">
+      <c r="E5">
         <v>115</v>
       </c>
     </row>
@@ -7881,12 +7874,10 @@
       <c r="A6" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B6" s="4"/>
-      <c r="C6" s="4">
+      <c r="C6">
         <v>87</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4">
+      <c r="E6">
         <v>87</v>
       </c>
     </row>
@@ -7894,16 +7885,16 @@
       <c r="A7" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B7" s="4">
+      <c r="B7">
         <v>23</v>
       </c>
-      <c r="C7" s="4">
+      <c r="C7">
         <v>2</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D7">
         <v>13</v>
       </c>
-      <c r="E7" s="4">
+      <c r="E7">
         <v>38</v>
       </c>
     </row>
@@ -7911,16 +7902,16 @@
       <c r="A8" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B8" s="4">
+      <c r="B8">
         <v>137</v>
       </c>
-      <c r="C8" s="4">
+      <c r="C8">
         <v>89</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8">
         <v>14</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8">
         <v>240</v>
       </c>
     </row>
@@ -7953,14 +7944,13 @@
       <c r="A16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="4">
+      <c r="B16">
         <v>99</v>
       </c>
-      <c r="C16" s="4">
+      <c r="C16">
         <v>16</v>
       </c>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4">
+      <c r="E16">
         <v>115</v>
       </c>
     </row>
@@ -7968,14 +7958,13 @@
       <c r="A17" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="4"/>
-      <c r="C17" s="4">
+      <c r="C17">
         <v>63</v>
       </c>
-      <c r="D17" s="4">
+      <c r="D17">
         <v>24</v>
       </c>
-      <c r="E17" s="4">
+      <c r="E17">
         <v>87</v>
       </c>
     </row>
@@ -7983,14 +7972,13 @@
       <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="4">
+      <c r="B18">
         <v>11</v>
       </c>
-      <c r="C18" s="4">
+      <c r="C18">
         <v>27</v>
       </c>
-      <c r="D18" s="4"/>
-      <c r="E18" s="4">
+      <c r="E18">
         <v>38</v>
       </c>
     </row>
@@ -7998,16 +7986,16 @@
       <c r="A19" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B19" s="4">
+      <c r="B19">
         <v>110</v>
       </c>
-      <c r="C19" s="4">
+      <c r="C19">
         <v>106</v>
       </c>
-      <c r="D19" s="4">
+      <c r="D19">
         <v>24</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19">
         <v>240</v>
       </c>
     </row>
@@ -8040,12 +8028,10 @@
       <c r="A26" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B26" s="4">
+      <c r="B26">
         <v>110</v>
       </c>
-      <c r="C26" s="4"/>
-      <c r="D26" s="4"/>
-      <c r="E26" s="4">
+      <c r="E26">
         <v>110</v>
       </c>
     </row>
@@ -8053,12 +8039,10 @@
       <c r="A27" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4">
+      <c r="C27">
         <v>24</v>
       </c>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4">
+      <c r="E27">
         <v>24</v>
       </c>
     </row>
@@ -8066,16 +8050,16 @@
       <c r="A28" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B28" s="4">
+      <c r="B28">
         <v>27</v>
       </c>
-      <c r="C28" s="4">
+      <c r="C28">
         <v>65</v>
       </c>
-      <c r="D28" s="4">
+      <c r="D28">
         <v>14</v>
       </c>
-      <c r="E28" s="4">
+      <c r="E28">
         <v>106</v>
       </c>
     </row>
@@ -8083,16 +8067,16 @@
       <c r="A29" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B29" s="4">
+      <c r="B29">
         <v>137</v>
       </c>
-      <c r="C29" s="4">
+      <c r="C29">
         <v>89</v>
       </c>
-      <c r="D29" s="4">
+      <c r="D29">
         <v>14</v>
       </c>
-      <c r="E29" s="4">
+      <c r="E29">
         <v>240</v>
       </c>
     </row>
@@ -8125,14 +8109,13 @@
       <c r="A36" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B36" s="4">
+      <c r="B36">
         <v>114</v>
       </c>
-      <c r="C36" s="4"/>
-      <c r="D36" s="4">
+      <c r="D36">
         <v>1</v>
       </c>
-      <c r="E36" s="4">
+      <c r="E36">
         <v>115</v>
       </c>
     </row>
@@ -8140,12 +8123,10 @@
       <c r="A37" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4">
+      <c r="C37">
         <v>87</v>
       </c>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4">
+      <c r="E37">
         <v>87</v>
       </c>
     </row>
@@ -8153,16 +8134,16 @@
       <c r="A38" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B38" s="4">
+      <c r="B38">
         <v>23</v>
       </c>
-      <c r="C38" s="4">
+      <c r="C38">
         <v>2</v>
       </c>
-      <c r="D38" s="4">
+      <c r="D38">
         <v>13</v>
       </c>
-      <c r="E38" s="4">
+      <c r="E38">
         <v>38</v>
       </c>
     </row>
@@ -8170,16 +8151,16 @@
       <c r="A39" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39">
         <v>137</v>
       </c>
-      <c r="C39" s="4">
+      <c r="C39">
         <v>89</v>
       </c>
-      <c r="D39" s="4">
+      <c r="D39">
         <v>14</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39">
         <v>240</v>
       </c>
     </row>
@@ -8208,78 +8189,78 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
+      <c r="A1" s="5" t="s">
         <v>492</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="E1" s="5" t="s">
         <v>489</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="5" t="s">
         <v>490</v>
       </c>
-      <c r="G1" s="6" t="s">
+      <c r="G1" s="5" t="s">
         <v>488</v>
       </c>
-      <c r="H1" s="6" t="s">
+      <c r="H1" s="5" t="s">
         <v>487</v>
       </c>
-      <c r="I1" s="6" t="s">
+      <c r="I1" s="5" t="s">
         <v>246</v>
       </c>
-      <c r="J1" s="6" t="s">
+      <c r="J1" s="5" t="s">
         <v>738</v>
       </c>
-      <c r="K1" s="6" t="s">
+      <c r="K1" s="5" t="s">
         <v>739</v>
       </c>
-      <c r="L1" s="6" t="s">
+      <c r="L1" s="5" t="s">
         <v>740</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C2" s="5">
+      <c r="B2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="4">
         <v>0.37188053100000001</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="E2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F2" s="5">
+      <c r="E2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F2" s="4">
         <v>1.1147499084472601E-2</v>
       </c>
-      <c r="G2" s="5" t="s">
+      <c r="G2" s="4" t="s">
         <v>247</v>
       </c>
-      <c r="H2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="H2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I2" s="4">
         <v>2.3912191390991201E-2</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="4" t="s">
         <v>498</v>
       </c>
-      <c r="K2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="5">
+      <c r="K2" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="4">
         <v>1.6514539718627898E-2</v>
       </c>
     </row>
@@ -8322,40 +8303,40 @@
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5">
+      <c r="B4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="4">
         <v>0.36285281200000002</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="E4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" s="5">
+      <c r="E4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" s="4">
         <v>1.1101245880126899E-2</v>
       </c>
-      <c r="G4" s="5" t="s">
+      <c r="G4" s="4" t="s">
         <v>249</v>
       </c>
-      <c r="H4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I4" s="5">
+      <c r="H4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I4" s="4">
         <v>1.42593383789062E-2</v>
       </c>
-      <c r="J4" s="5" t="s">
+      <c r="J4" s="4" t="s">
         <v>500</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L4" s="5">
+      <c r="K4" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L4" s="4">
         <v>1.6354560852050701E-2</v>
       </c>
     </row>
@@ -8398,40 +8379,40 @@
       </c>
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="4">
         <v>0.33942174899999999</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="E6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F6" s="5">
+      <c r="E6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F6" s="4">
         <v>1.18434429168701E-2</v>
       </c>
-      <c r="G6" s="5" t="s">
+      <c r="G6" s="4" t="s">
         <v>251</v>
       </c>
-      <c r="H6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="H6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="4">
         <v>1.4382362365722601E-2</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="4" t="s">
         <v>502</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L6" s="5">
+      <c r="K6" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L6" s="4">
         <v>1.7436504364013599E-2</v>
       </c>
     </row>
@@ -8474,40 +8455,40 @@
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C8" s="5">
+      <c r="B8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C8" s="4">
         <v>0.35577321099999998</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="E8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F8" s="5">
+      <c r="E8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F8" s="4">
         <v>1.02019309997558E-2</v>
       </c>
-      <c r="G8" s="5" t="s">
+      <c r="G8" s="4" t="s">
         <v>253</v>
       </c>
-      <c r="H8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="H8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I8" s="4">
         <v>1.8209457397460899E-2</v>
       </c>
-      <c r="J8" s="5" t="s">
+      <c r="J8" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L8" s="5">
+      <c r="K8" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L8" s="4">
         <v>1.7031669616699201E-2</v>
       </c>
     </row>
@@ -8550,40 +8531,40 @@
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C10" s="5">
+      <c r="B10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C10" s="4">
         <v>0.47258138700000002</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="E10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F10" s="5">
+      <c r="E10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F10" s="4">
         <v>1.14903450012207E-2</v>
       </c>
-      <c r="G10" s="5" t="s">
+      <c r="G10" s="4" t="s">
         <v>255</v>
       </c>
-      <c r="H10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="4">
         <v>1.6896009445190398E-2</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="4" t="s">
         <v>506</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L10" s="5">
+      <c r="K10" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L10" s="4">
         <v>2.0154476165771401E-2</v>
       </c>
     </row>
@@ -8626,40 +8607,40 @@
       </c>
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C12" s="5">
+      <c r="B12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C12" s="4">
         <v>0.45357346500000001</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="E12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F12" s="5">
+      <c r="E12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F12" s="4">
         <v>1.04813575744628E-2</v>
       </c>
-      <c r="G12" s="5" t="s">
+      <c r="G12" s="4" t="s">
         <v>257</v>
       </c>
-      <c r="H12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="H12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I12" s="4">
         <v>1.46124362945556E-2</v>
       </c>
-      <c r="J12" s="5" t="s">
+      <c r="J12" s="4" t="s">
         <v>508</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L12" s="5">
+      <c r="K12" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L12" s="4">
         <v>2.36668586730957E-2</v>
       </c>
     </row>
@@ -8702,40 +8683,40 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C14" s="5">
+      <c r="B14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C14" s="4">
         <v>0.35235786400000002</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F14" s="5">
+      <c r="E14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F14" s="4">
         <v>1.2101650238037101E-2</v>
       </c>
-      <c r="G14" s="5" t="s">
+      <c r="G14" s="4" t="s">
         <v>259</v>
       </c>
-      <c r="H14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="5">
+      <c r="H14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="4">
         <v>1.36873722076416E-2</v>
       </c>
-      <c r="J14" s="5" t="s">
+      <c r="J14" s="4" t="s">
         <v>510</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L14" s="5">
+      <c r="K14" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L14" s="4">
         <v>2.06084251403808E-2</v>
       </c>
     </row>
@@ -8778,40 +8759,40 @@
       </c>
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C16" s="5">
+      <c r="B16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C16" s="4">
         <v>0.470790863</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="E16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F16" s="5">
+      <c r="E16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F16" s="4">
         <v>1.3822555541992101E-2</v>
       </c>
-      <c r="G16" s="5" t="s">
+      <c r="G16" s="4" t="s">
         <v>261</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I16" s="5">
+      <c r="H16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I16" s="4">
         <v>1.5658855438232401E-2</v>
       </c>
-      <c r="J16" s="5" t="s">
+      <c r="J16" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L16" s="5">
+      <c r="K16" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L16" s="4">
         <v>1.7662525177001901E-2</v>
       </c>
     </row>
@@ -8854,40 +8835,40 @@
       </c>
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C18" s="5">
+      <c r="B18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C18" s="4">
         <v>1.2625391480000001</v>
       </c>
-      <c r="D18" s="5" t="s">
+      <c r="D18" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="E18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F18" s="5">
+      <c r="E18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F18" s="4">
         <v>1.2144327163696201E-2</v>
       </c>
-      <c r="G18" s="5" t="s">
+      <c r="G18" s="4" t="s">
         <v>263</v>
       </c>
-      <c r="H18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="5">
+      <c r="H18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="4">
         <v>1.6456604003906201E-2</v>
       </c>
-      <c r="J18" s="5" t="s">
+      <c r="J18" s="4" t="s">
         <v>514</v>
       </c>
-      <c r="K18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L18" s="5">
+      <c r="K18" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L18" s="4">
         <v>1.7219066619872998E-2</v>
       </c>
     </row>
@@ -8930,40 +8911,40 @@
       </c>
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C20" s="5">
+      <c r="B20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C20" s="4">
         <v>0.47560358000000003</v>
       </c>
-      <c r="D20" s="5" t="s">
+      <c r="D20" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F20" s="5">
+      <c r="E20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F20" s="4">
         <v>1.39992237091064E-2</v>
       </c>
-      <c r="G20" s="5" t="s">
+      <c r="G20" s="4" t="s">
         <v>265</v>
       </c>
-      <c r="H20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I20" s="5">
+      <c r="H20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I20" s="4">
         <v>1.6952276229858398E-2</v>
       </c>
-      <c r="J20" s="5" t="s">
+      <c r="J20" s="4" t="s">
         <v>516</v>
       </c>
-      <c r="K20" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L20" s="5">
+      <c r="K20" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L20" s="4">
         <v>2.0709753036498999E-2</v>
       </c>
     </row>
@@ -9006,40 +8987,40 @@
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="5" t="s">
+      <c r="B22" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C22" s="5">
+      <c r="C22" s="4">
         <v>0.171948671</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="D22" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="E22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" s="5">
+      <c r="E22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F22" s="4">
         <v>1.08845233917236E-2</v>
       </c>
-      <c r="G22" s="5" t="s">
+      <c r="G22" s="4" t="s">
         <v>267</v>
       </c>
-      <c r="H22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I22" s="5">
+      <c r="H22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I22" s="4">
         <v>6.8573951721191398E-3</v>
       </c>
-      <c r="J22" s="5" t="s">
+      <c r="J22" s="4" t="s">
         <v>518</v>
       </c>
-      <c r="K22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L22" s="5">
+      <c r="K22" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L22" s="4">
         <v>1.14033222198486E-2</v>
       </c>
     </row>
@@ -9082,40 +9063,40 @@
       </c>
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B24" s="5" t="s">
+      <c r="B24" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C24" s="5">
+      <c r="C24" s="4">
         <v>0.17573070499999999</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="D24" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="E24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F24" s="5">
+      <c r="E24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F24" s="4">
         <v>1.0511159896850499E-2</v>
       </c>
-      <c r="G24" s="5" t="s">
+      <c r="G24" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="H24" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I24" s="5">
+      <c r="H24" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I24" s="4">
         <v>51.387100219726499</v>
       </c>
-      <c r="J24" s="5" t="s">
+      <c r="J24" s="4" t="s">
         <v>520</v>
       </c>
-      <c r="K24" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L24" s="5">
+      <c r="K24" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L24" s="4">
         <v>1.20236873626708E-2</v>
       </c>
     </row>
@@ -9158,40 +9139,40 @@
       </c>
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="4" t="s">
         <v>30</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C26" s="5">
+      <c r="B26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C26" s="4">
         <v>0.35530591</v>
       </c>
-      <c r="D26" s="5" t="s">
+      <c r="D26" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="E26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F26" s="5">
+      <c r="E26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F26" s="4">
         <v>1.97243690490722E-2</v>
       </c>
-      <c r="G26" s="5" t="s">
+      <c r="G26" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="5">
+      <c r="H26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="4">
         <v>1.43196582794189E-2</v>
       </c>
-      <c r="J26" s="5" t="s">
+      <c r="J26" s="4" t="s">
         <v>522</v>
       </c>
-      <c r="K26" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L26" s="5">
+      <c r="K26" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L26" s="4">
         <v>1.83415412902832E-2</v>
       </c>
     </row>
@@ -9234,40 +9215,40 @@
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="5">
+      <c r="B28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C28" s="4">
         <v>0.37428951300000002</v>
       </c>
-      <c r="D28" s="5" t="s">
+      <c r="D28" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="E28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F28" s="5">
+      <c r="E28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F28" s="4">
         <v>1.09543800354003E-2</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="H28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I28" s="5">
+      <c r="H28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I28" s="4">
         <v>1.4606237411498999E-2</v>
       </c>
-      <c r="J28" s="5" t="s">
+      <c r="J28" s="4" t="s">
         <v>524</v>
       </c>
-      <c r="K28" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L28" s="5">
+      <c r="K28" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L28" s="4">
         <v>1.8390655517578101E-2</v>
       </c>
     </row>
@@ -9310,40 +9291,40 @@
       </c>
     </row>
     <row r="30" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C30" s="5">
+      <c r="B30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C30" s="4">
         <v>0.40168189999999998</v>
       </c>
-      <c r="D30" s="5" t="s">
+      <c r="D30" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="E30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F30" s="5">
+      <c r="E30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F30" s="4">
         <v>1.7477989196777299E-2</v>
       </c>
-      <c r="G30" s="5" t="s">
+      <c r="G30" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="H30" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I30" s="5">
+      <c r="H30" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I30" s="4">
         <v>54.586651802062903</v>
       </c>
-      <c r="J30" s="5" t="s">
+      <c r="J30" s="4" t="s">
         <v>526</v>
       </c>
-      <c r="K30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L30" s="5">
+      <c r="K30" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L30" s="4">
         <v>2.63903141021728E-2</v>
       </c>
     </row>
@@ -9386,40 +9367,40 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C32" s="5">
+      <c r="B32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C32" s="4">
         <v>0.38092088699999999</v>
       </c>
-      <c r="D32" s="5" t="s">
+      <c r="D32" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="E32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F32" s="5">
+      <c r="E32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F32" s="4">
         <v>1.12445354461669E-2</v>
       </c>
-      <c r="G32" s="5" t="s">
+      <c r="G32" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="H32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I32" s="5">
+      <c r="H32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I32" s="4">
         <v>1.62906646728515E-2</v>
       </c>
-      <c r="J32" s="5" t="s">
+      <c r="J32" s="4" t="s">
         <v>528</v>
       </c>
-      <c r="K32" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L32" s="5">
+      <c r="K32" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L32" s="4">
         <v>1.7621994018554601E-2</v>
       </c>
     </row>
@@ -9462,40 +9443,40 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C34" s="5">
+      <c r="B34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C34" s="4">
         <v>0.36356306100000002</v>
       </c>
-      <c r="D34" s="5" t="s">
+      <c r="D34" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="E34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F34" s="5">
+      <c r="E34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F34" s="4">
         <v>1.2879133224487299E-2</v>
       </c>
-      <c r="G34" s="5" t="s">
+      <c r="G34" s="4" t="s">
         <v>279</v>
       </c>
-      <c r="H34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I34" s="5">
+      <c r="H34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="4">
         <v>1.64568424224853E-2</v>
       </c>
-      <c r="J34" s="5" t="s">
+      <c r="J34" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="K34" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L34" s="5">
+      <c r="K34" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L34" s="4">
         <v>1.91776752471923E-2</v>
       </c>
     </row>
@@ -9538,40 +9519,40 @@
       </c>
     </row>
     <row r="36" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C36" s="5">
+      <c r="B36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C36" s="4">
         <v>0.37942028</v>
       </c>
-      <c r="D36" s="5" t="s">
+      <c r="D36" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="E36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F36" s="5">
+      <c r="E36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F36" s="4">
         <v>1.16040706634521E-2</v>
       </c>
-      <c r="G36" s="5" t="s">
+      <c r="G36" s="4" t="s">
         <v>281</v>
       </c>
-      <c r="H36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I36" s="5">
+      <c r="H36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I36" s="4">
         <v>1.3952970504760701E-2</v>
       </c>
-      <c r="J36" s="5" t="s">
+      <c r="J36" s="4" t="s">
         <v>532</v>
       </c>
-      <c r="K36" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L36" s="5">
+      <c r="K36" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L36" s="4">
         <v>1.63538455963134E-2</v>
       </c>
     </row>
@@ -9614,40 +9595,40 @@
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C38" s="5">
+      <c r="B38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C38" s="4">
         <v>0.35112977000000001</v>
       </c>
-      <c r="D38" s="5" t="s">
+      <c r="D38" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="E38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F38" s="5">
+      <c r="E38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F38" s="4">
         <v>1.13215446472167E-2</v>
       </c>
-      <c r="G38" s="5" t="s">
+      <c r="G38" s="4" t="s">
         <v>283</v>
       </c>
-      <c r="H38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="5">
+      <c r="H38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="4">
         <v>1.48520469665527E-2</v>
       </c>
-      <c r="J38" s="5" t="s">
+      <c r="J38" s="4" t="s">
         <v>534</v>
       </c>
-      <c r="K38" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L38" s="5">
+      <c r="K38" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L38" s="4">
         <v>1.69494152069091E-2</v>
       </c>
     </row>
@@ -9690,40 +9671,40 @@
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="B40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C40" s="5">
+      <c r="B40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C40" s="4">
         <v>0.34739613499999999</v>
       </c>
-      <c r="D40" s="5" t="s">
+      <c r="D40" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="E40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F40" s="5">
+      <c r="E40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F40" s="4">
         <v>1.1582612991332999E-2</v>
       </c>
-      <c r="G40" s="5" t="s">
+      <c r="G40" s="4" t="s">
         <v>285</v>
       </c>
-      <c r="H40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I40" s="5">
+      <c r="H40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I40" s="4">
         <v>1.4809131622314399E-2</v>
       </c>
-      <c r="J40" s="5" t="s">
+      <c r="J40" s="4" t="s">
         <v>536</v>
       </c>
-      <c r="K40" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L40" s="5">
+      <c r="K40" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L40" s="4">
         <v>1.7155408859252898E-2</v>
       </c>
     </row>
@@ -9766,40 +9747,40 @@
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="B42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C42" s="5">
+      <c r="B42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C42" s="4">
         <v>0.37474799199999997</v>
       </c>
-      <c r="D42" s="5" t="s">
+      <c r="D42" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="E42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F42" s="5">
+      <c r="E42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F42" s="4">
         <v>1.32601261138916E-2</v>
       </c>
-      <c r="G42" s="5" t="s">
+      <c r="G42" s="4" t="s">
         <v>287</v>
       </c>
-      <c r="H42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="5">
+      <c r="H42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="4">
         <v>1.46450996398925E-2</v>
       </c>
-      <c r="J42" s="5" t="s">
+      <c r="J42" s="4" t="s">
         <v>538</v>
       </c>
-      <c r="K42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L42" s="5">
+      <c r="K42" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L42" s="4">
         <v>1.7924070358276301E-2</v>
       </c>
     </row>
@@ -9842,40 +9823,40 @@
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="B44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C44" s="5">
+      <c r="B44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C44" s="4">
         <v>0.28431868599999999</v>
       </c>
-      <c r="D44" s="5" t="s">
+      <c r="D44" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="E44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F44" s="5">
+      <c r="E44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F44" s="4">
         <v>1.2367725372314399E-2</v>
       </c>
-      <c r="G44" s="5" t="s">
+      <c r="G44" s="4" t="s">
         <v>289</v>
       </c>
-      <c r="H44" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I44" s="5">
+      <c r="H44" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I44" s="4">
         <v>55.6835806369781</v>
       </c>
-      <c r="J44" s="5" t="s">
+      <c r="J44" s="4" t="s">
         <v>540</v>
       </c>
-      <c r="K44" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L44" s="5">
+      <c r="K44" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L44" s="4">
         <v>2.0246744155883699E-2</v>
       </c>
     </row>
@@ -9918,40 +9899,40 @@
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="B46" s="5" t="s">
+      <c r="B46" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C46" s="5">
+      <c r="C46" s="4">
         <v>0.24760079400000001</v>
       </c>
-      <c r="D46" s="5" t="s">
+      <c r="D46" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="E46" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F46" s="5">
+      <c r="E46" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F46" s="4">
         <v>2.0121812820434501E-2</v>
       </c>
-      <c r="G46" s="5" t="s">
+      <c r="G46" s="4" t="s">
         <v>291</v>
       </c>
-      <c r="H46" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I46" s="5">
+      <c r="H46" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I46" s="4">
         <v>51.874607086181598</v>
       </c>
-      <c r="J46" s="5" t="s">
+      <c r="J46" s="4" t="s">
         <v>542</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L46" s="5">
+      <c r="K46" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L46" s="4">
         <v>2.2209167480468701E-2</v>
       </c>
     </row>
@@ -9994,40 +9975,40 @@
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="B48" s="5" t="s">
+      <c r="B48" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C48" s="5">
+      <c r="C48" s="4">
         <v>0.25509429</v>
       </c>
-      <c r="D48" s="5" t="s">
+      <c r="D48" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="E48" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F48" s="5">
+      <c r="E48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F48" s="4">
         <v>2.0133495330810498E-2</v>
       </c>
-      <c r="G48" s="5" t="s">
+      <c r="G48" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="H48" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I48" s="5">
+      <c r="H48" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I48" s="4">
         <v>55.451035499572697</v>
       </c>
-      <c r="J48" s="5" t="s">
+      <c r="J48" s="4" t="s">
         <v>544</v>
       </c>
-      <c r="K48" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L48" s="5">
+      <c r="K48" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L48" s="4">
         <v>2.2112846374511701E-2</v>
       </c>
     </row>
@@ -10070,40 +10051,40 @@
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="4" t="s">
         <v>54</v>
       </c>
-      <c r="B50" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C50" s="5">
+      <c r="B50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C50" s="4">
         <v>0.23722600899999999</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="E50" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F50" s="5">
+      <c r="E50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F50" s="4">
         <v>2.1967649459838801E-2</v>
       </c>
-      <c r="G50" s="5" t="s">
+      <c r="G50" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="H50" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I50" s="5">
+      <c r="H50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="4">
         <v>4.1394233703613198E-2</v>
       </c>
-      <c r="J50" s="5" t="s">
+      <c r="J50" s="4" t="s">
         <v>546</v>
       </c>
-      <c r="K50" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L50" s="5">
+      <c r="K50" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L50" s="4">
         <v>3.6201000213622998E-2</v>
       </c>
     </row>
@@ -10146,40 +10127,40 @@
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A52" s="5" t="s">
+      <c r="A52" s="4" t="s">
         <v>56</v>
       </c>
-      <c r="B52" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C52" s="5">
+      <c r="B52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C52" s="4">
         <v>0.53693818999999998</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="E52" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F52" s="5">
+      <c r="E52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F52" s="4">
         <v>1.28600597381591E-2</v>
       </c>
-      <c r="G52" s="5" t="s">
+      <c r="G52" s="4" t="s">
         <v>297</v>
       </c>
-      <c r="H52" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I52" s="5">
+      <c r="H52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I52" s="4">
         <v>3.0047893524169901E-2</v>
       </c>
-      <c r="J52" s="5" t="s">
+      <c r="J52" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="K52" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L52" s="5">
+      <c r="K52" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L52" s="4">
         <v>2.08067893981933E-2</v>
       </c>
     </row>
@@ -10222,40 +10203,40 @@
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A54" s="5" t="s">
+      <c r="A54" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="B54" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C54" s="5">
+      <c r="B54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C54" s="4">
         <v>0.45150470700000001</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="E54" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F54" s="5">
+      <c r="E54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F54" s="4">
         <v>1.8323421478271401E-2</v>
       </c>
-      <c r="G54" s="5" t="s">
+      <c r="G54" s="4" t="s">
         <v>299</v>
       </c>
-      <c r="H54" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I54" s="5">
+      <c r="H54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I54" s="4">
         <v>4.2010545730590799E-2</v>
       </c>
-      <c r="J54" s="5" t="s">
+      <c r="J54" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="K54" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L54" s="5">
+      <c r="K54" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L54" s="4">
         <v>3.5653591156005797E-2</v>
       </c>
     </row>
@@ -10298,40 +10279,40 @@
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A56" s="5" t="s">
+      <c r="A56" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C56" s="5">
+      <c r="C56" s="4">
         <v>0.19108367000000001</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="E56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F56" s="5">
+      <c r="E56" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F56" s="4">
         <v>1.0351657867431601E-2</v>
       </c>
-      <c r="G56" s="5" t="s">
+      <c r="G56" s="4" t="s">
         <v>301</v>
       </c>
-      <c r="H56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I56" s="5">
+      <c r="H56" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I56" s="4">
         <v>6.1297416687011701E-3</v>
       </c>
-      <c r="J56" s="5" t="s">
+      <c r="J56" s="4" t="s">
         <v>552</v>
       </c>
-      <c r="K56" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L56" s="5">
+      <c r="K56" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L56" s="4">
         <v>1.11615657806396E-2</v>
       </c>
     </row>
@@ -10374,40 +10355,40 @@
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A58" s="5" t="s">
+      <c r="A58" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="B58" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C58" s="5">
+      <c r="B58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C58" s="4">
         <v>0.43476986899999998</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="E58" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F58" s="5">
+      <c r="E58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F58" s="4">
         <v>1.31189823150634E-2</v>
       </c>
-      <c r="G58" s="5" t="s">
+      <c r="G58" s="4" t="s">
         <v>303</v>
       </c>
-      <c r="H58" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I58" s="5">
+      <c r="H58" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I58" s="4">
         <v>55.479140996932898</v>
       </c>
-      <c r="J58" s="5" t="s">
+      <c r="J58" s="4" t="s">
         <v>554</v>
       </c>
-      <c r="K58" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L58" s="5">
+      <c r="K58" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L58" s="4">
         <v>2.05068588256835E-2</v>
       </c>
     </row>
@@ -10450,40 +10431,40 @@
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A60" s="5" t="s">
+      <c r="A60" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C60" s="5">
+      <c r="C60" s="4">
         <v>0.18275475499999999</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="E60" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F60" s="5">
+      <c r="E60" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F60" s="4">
         <v>1.09434127807617E-2</v>
       </c>
-      <c r="G60" s="5" t="s">
+      <c r="G60" s="4" t="s">
         <v>305</v>
       </c>
-      <c r="H60" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I60" s="5">
+      <c r="H60" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I60" s="4">
         <v>5.5794715881347604E-3</v>
       </c>
-      <c r="J60" s="5" t="s">
+      <c r="J60" s="4" t="s">
         <v>556</v>
       </c>
-      <c r="K60" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L60" s="5">
+      <c r="K60" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L60" s="4">
         <v>1.0702133178710899E-2</v>
       </c>
     </row>
@@ -10526,40 +10507,40 @@
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A62" s="5" t="s">
+      <c r="A62" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C62" s="5">
+      <c r="C62" s="4">
         <v>0.27372598599999998</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="E62" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F62" s="5">
+      <c r="E62" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F62" s="4">
         <v>1.8664360046386701E-2</v>
       </c>
-      <c r="G62" s="5" t="s">
+      <c r="G62" s="4" t="s">
         <v>307</v>
       </c>
-      <c r="H62" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I62" s="5">
+      <c r="H62" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I62" s="4">
         <v>54.932330608367899</v>
       </c>
-      <c r="J62" s="5" t="s">
+      <c r="J62" s="4" t="s">
         <v>558</v>
       </c>
-      <c r="K62" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L62" s="5">
+      <c r="K62" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L62" s="4">
         <v>1.9378662109375E-2</v>
       </c>
     </row>
@@ -10602,40 +10583,40 @@
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A64" s="5" t="s">
+      <c r="A64" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="B64" s="5" t="s">
+      <c r="B64" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C64" s="5">
+      <c r="C64" s="4">
         <v>1.031116009</v>
       </c>
-      <c r="D64" s="5" t="s">
+      <c r="D64" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="E64" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F64" s="5">
+      <c r="E64" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F64" s="4">
         <v>1.8509149551391602E-2</v>
       </c>
-      <c r="G64" s="5" t="s">
+      <c r="G64" s="4" t="s">
         <v>309</v>
       </c>
-      <c r="H64" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I64" s="5">
+      <c r="H64" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I64" s="4">
         <v>54.8098945617675</v>
       </c>
-      <c r="J64" s="5" t="s">
+      <c r="J64" s="4" t="s">
         <v>560</v>
       </c>
-      <c r="K64" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L64" s="5">
+      <c r="K64" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L64" s="4">
         <v>1.89404487609863E-2</v>
       </c>
     </row>
@@ -10678,40 +10659,40 @@
       </c>
     </row>
     <row r="66" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A66" s="5" t="s">
+      <c r="A66" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="B66" s="5" t="s">
+      <c r="B66" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C66" s="5">
+      <c r="C66" s="4">
         <v>0.25124216100000002</v>
       </c>
-      <c r="D66" s="5" t="s">
+      <c r="D66" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="E66" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F66" s="5">
+      <c r="E66" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F66" s="4">
         <v>2.0653486251830999E-2</v>
       </c>
-      <c r="G66" s="5" t="s">
+      <c r="G66" s="4" t="s">
         <v>311</v>
       </c>
-      <c r="H66" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I66" s="5">
+      <c r="H66" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" s="4">
         <v>53.014360189437802</v>
       </c>
-      <c r="J66" s="5" t="s">
+      <c r="J66" s="4" t="s">
         <v>562</v>
       </c>
-      <c r="K66" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L66" s="5">
+      <c r="K66" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L66" s="4">
         <v>2.01210975646972E-2</v>
       </c>
     </row>
@@ -10754,40 +10735,40 @@
       </c>
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A68" s="5" t="s">
+      <c r="A68" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C68" s="5">
+      <c r="C68" s="4">
         <v>0.27518415499999999</v>
       </c>
-      <c r="D68" s="5" t="s">
+      <c r="D68" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="E68" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F68" s="5">
+      <c r="E68" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F68" s="4">
         <v>2.0099878311157199E-2</v>
       </c>
-      <c r="G68" s="5" t="s">
+      <c r="G68" s="4" t="s">
         <v>313</v>
       </c>
-      <c r="H68" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I68" s="5">
+      <c r="H68" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I68" s="4">
         <v>55.357839345932</v>
       </c>
-      <c r="J68" s="5" t="s">
+      <c r="J68" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="K68" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L68" s="5">
+      <c r="K68" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L68" s="4">
         <v>1.9072771072387602E-2</v>
       </c>
     </row>
@@ -10830,40 +10811,40 @@
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A70" s="5" t="s">
+      <c r="A70" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B70" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C70" s="5">
+      <c r="B70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C70" s="4">
         <v>0.41223072999999999</v>
       </c>
-      <c r="D70" s="5" t="s">
+      <c r="D70" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="E70" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F70" s="5">
+      <c r="E70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F70" s="4">
         <v>1.18813514709472E-2</v>
       </c>
-      <c r="G70" s="5" t="s">
+      <c r="G70" s="4" t="s">
         <v>315</v>
       </c>
-      <c r="H70" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I70" s="5">
+      <c r="H70" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I70" s="4">
         <v>55.566439628601003</v>
       </c>
-      <c r="J70" s="5" t="s">
+      <c r="J70" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="K70" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L70" s="5">
+      <c r="K70" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L70" s="4">
         <v>2.1231174468994099E-2</v>
       </c>
     </row>
@@ -10906,40 +10887,40 @@
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="B72" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C72" s="5">
+      <c r="B72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C72" s="4">
         <v>0.21952915200000001</v>
       </c>
-      <c r="D72" s="5" t="s">
+      <c r="D72" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="E72" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F72" s="5">
+      <c r="E72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F72" s="4">
         <v>1.37982368469238E-2</v>
       </c>
-      <c r="G72" s="5" t="s">
+      <c r="G72" s="4" t="s">
         <v>317</v>
       </c>
-      <c r="H72" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I72" s="5">
+      <c r="H72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I72" s="4">
         <v>3.0277252197265601E-2</v>
       </c>
-      <c r="J72" s="5" t="s">
+      <c r="J72" s="4" t="s">
         <v>568</v>
       </c>
-      <c r="K72" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L72" s="5">
+      <c r="K72" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L72" s="4">
         <v>2.0170450210571199E-2</v>
       </c>
     </row>
@@ -10982,40 +10963,40 @@
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B74" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C74" s="5">
+      <c r="B74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C74" s="4">
         <v>0.14899373099999999</v>
       </c>
-      <c r="D74" s="5" t="s">
+      <c r="D74" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="E74" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F74" s="5">
+      <c r="E74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F74" s="4">
         <v>1.36232376098632E-2</v>
       </c>
-      <c r="G74" s="5" t="s">
+      <c r="G74" s="4" t="s">
         <v>319</v>
       </c>
-      <c r="H74" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I74" s="5">
+      <c r="H74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I74" s="4">
         <v>1.6113519668579102E-2</v>
       </c>
-      <c r="J74" s="5" t="s">
+      <c r="J74" s="4" t="s">
         <v>570</v>
       </c>
-      <c r="K74" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L74" s="5">
+      <c r="K74" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L74" s="4">
         <v>2.7181386947631801E-2</v>
       </c>
     </row>
@@ -11058,40 +11039,40 @@
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A76" s="5" t="s">
+      <c r="A76" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="B76" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C76" s="5">
+      <c r="B76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C76" s="4">
         <v>0.21307730699999999</v>
       </c>
-      <c r="D76" s="5" t="s">
+      <c r="D76" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="E76" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F76" s="5">
+      <c r="E76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F76" s="4">
         <v>1.54056549072265E-2</v>
       </c>
-      <c r="G76" s="5" t="s">
+      <c r="G76" s="4" t="s">
         <v>321</v>
       </c>
-      <c r="H76" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I76" s="5">
+      <c r="H76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I76" s="4">
         <v>2.9445648193359299E-2</v>
       </c>
-      <c r="J76" s="5" t="s">
+      <c r="J76" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="K76" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L76" s="5">
+      <c r="K76" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L76" s="4">
         <v>2.22437381744384E-2</v>
       </c>
     </row>
@@ -11134,40 +11115,40 @@
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A78" s="5" t="s">
+      <c r="A78" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="B78" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C78" s="5">
+      <c r="B78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C78" s="4">
         <v>0.52924394600000002</v>
       </c>
-      <c r="D78" s="5" t="s">
+      <c r="D78" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="E78" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F78" s="5">
+      <c r="E78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F78" s="4">
         <v>1.7548799514770501E-2</v>
       </c>
-      <c r="G78" s="5" t="s">
+      <c r="G78" s="4" t="s">
         <v>323</v>
       </c>
-      <c r="H78" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I78" s="5">
+      <c r="H78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I78" s="4">
         <v>3.6362171173095703E-2</v>
       </c>
-      <c r="J78" s="5" t="s">
+      <c r="J78" s="4" t="s">
         <v>574</v>
       </c>
-      <c r="K78" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L78" s="5">
+      <c r="K78" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L78" s="4">
         <v>2.6474237442016602E-2</v>
       </c>
     </row>
@@ -11210,40 +11191,40 @@
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A80" s="5" t="s">
+      <c r="A80" s="4" t="s">
         <v>84</v>
       </c>
-      <c r="B80" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C80" s="5">
+      <c r="B80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C80" s="4">
         <v>0.50703883199999999</v>
       </c>
-      <c r="D80" s="5" t="s">
+      <c r="D80" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="E80" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F80" s="5">
+      <c r="E80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F80" s="4">
         <v>1.69262886047363E-2</v>
       </c>
-      <c r="G80" s="5" t="s">
+      <c r="G80" s="4" t="s">
         <v>325</v>
       </c>
-      <c r="H80" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I80" s="5">
+      <c r="H80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I80" s="4">
         <v>1.5881061553954998E-2</v>
       </c>
-      <c r="J80" s="5" t="s">
+      <c r="J80" s="4" t="s">
         <v>576</v>
       </c>
-      <c r="K80" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L80" s="5">
+      <c r="K80" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L80" s="4">
         <v>2.30333805084228E-2</v>
       </c>
     </row>
@@ -11286,40 +11267,40 @@
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A82" s="5" t="s">
+      <c r="A82" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="B82" s="5" t="s">
+      <c r="B82" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C82" s="5">
+      <c r="C82" s="4">
         <v>0.171390295</v>
       </c>
-      <c r="D82" s="5" t="s">
+      <c r="D82" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="E82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F82" s="5">
+      <c r="E82" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F82" s="4">
         <v>9.7887516021728498E-3</v>
       </c>
-      <c r="G82" s="5" t="s">
+      <c r="G82" s="4" t="s">
         <v>327</v>
       </c>
-      <c r="H82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I82" s="5">
+      <c r="H82" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I82" s="4">
         <v>5.5334568023681597E-3</v>
       </c>
-      <c r="J82" s="5" t="s">
+      <c r="J82" s="4" t="s">
         <v>578</v>
       </c>
-      <c r="K82" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L82" s="5">
+      <c r="K82" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L82" s="4">
         <v>9.8292827606201102E-3</v>
       </c>
     </row>
@@ -11362,40 +11343,40 @@
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A84" s="5" t="s">
+      <c r="A84" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="B84" s="5" t="s">
+      <c r="B84" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C84" s="5">
+      <c r="C84" s="4">
         <v>0.16839432700000001</v>
       </c>
-      <c r="D84" s="5" t="s">
+      <c r="D84" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="E84" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F84" s="5">
+      <c r="E84" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F84" s="4">
         <v>9.4184875488281198E-3</v>
       </c>
-      <c r="G84" s="5" t="s">
+      <c r="G84" s="4" t="s">
         <v>329</v>
       </c>
-      <c r="H84" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I84" s="5">
+      <c r="H84" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I84" s="4">
         <v>51.346651792526202</v>
       </c>
-      <c r="J84" s="5" t="s">
+      <c r="J84" s="4" t="s">
         <v>580</v>
       </c>
-      <c r="K84" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L84" s="5">
+      <c r="K84" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L84" s="4">
         <v>1.0740280151367101E-2</v>
       </c>
     </row>
@@ -11438,40 +11419,40 @@
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A86" s="5" t="s">
+      <c r="A86" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="B86" s="5" t="s">
+      <c r="B86" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C86" s="5">
+      <c r="C86" s="4">
         <v>0.26660466199999999</v>
       </c>
-      <c r="D86" s="5" t="s">
+      <c r="D86" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="E86" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F86" s="5">
+      <c r="E86" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F86" s="4">
         <v>1.9557476043701099E-2</v>
       </c>
-      <c r="G86" s="5" t="s">
+      <c r="G86" s="4" t="s">
         <v>331</v>
       </c>
-      <c r="H86" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I86" s="5">
+      <c r="H86" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I86" s="4">
         <v>55.607307672500603</v>
       </c>
-      <c r="J86" s="5" t="s">
+      <c r="J86" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="K86" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L86" s="5">
+      <c r="K86" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L86" s="4">
         <v>1.9451618194579998E-2</v>
       </c>
     </row>
@@ -11514,40 +11495,40 @@
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A88" s="5" t="s">
+      <c r="A88" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="4">
         <v>0.17417359399999999</v>
       </c>
-      <c r="D88" s="5" t="s">
+      <c r="D88" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="E88" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F88" s="5">
+      <c r="E88" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F88" s="4">
         <v>1.12631320953369E-2</v>
       </c>
-      <c r="G88" s="5" t="s">
+      <c r="G88" s="4" t="s">
         <v>333</v>
       </c>
-      <c r="H88" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I88" s="5">
+      <c r="H88" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I88" s="4">
         <v>6.3927173614501901E-3</v>
       </c>
-      <c r="J88" s="5" t="s">
+      <c r="J88" s="4" t="s">
         <v>584</v>
       </c>
-      <c r="K88" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L88" s="5">
+      <c r="K88" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L88" s="4">
         <v>1.0221242904662999E-2</v>
       </c>
     </row>
@@ -11590,40 +11571,40 @@
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A90" s="5" t="s">
+      <c r="A90" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="4">
         <v>0.25066876399999999</v>
       </c>
-      <c r="D90" s="5" t="s">
+      <c r="D90" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="E90" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F90" s="5">
+      <c r="E90" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F90" s="4">
         <v>2.0402193069458001E-2</v>
       </c>
-      <c r="G90" s="5" t="s">
+      <c r="G90" s="4" t="s">
         <v>335</v>
       </c>
-      <c r="H90" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I90" s="5">
+      <c r="H90" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I90" s="4">
         <v>54.823024749755803</v>
       </c>
-      <c r="J90" s="5" t="s">
+      <c r="J90" s="4" t="s">
         <v>586</v>
       </c>
-      <c r="K90" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L90" s="5">
+      <c r="K90" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L90" s="4">
         <v>2.1895170211791899E-2</v>
       </c>
     </row>
@@ -11666,40 +11647,40 @@
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A92" s="5" t="s">
+      <c r="A92" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="B92" s="5" t="s">
+      <c r="B92" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C92" s="5">
+      <c r="C92" s="4">
         <v>0.17218995100000001</v>
       </c>
-      <c r="D92" s="5" t="s">
+      <c r="D92" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="E92" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F92" s="5">
+      <c r="E92" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F92" s="4">
         <v>8.4898471832275304E-3</v>
       </c>
-      <c r="G92" s="5" t="s">
+      <c r="G92" s="4" t="s">
         <v>337</v>
       </c>
-      <c r="H92" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I92" s="5">
+      <c r="H92" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I92" s="4">
         <v>6.35123252868652E-3</v>
       </c>
-      <c r="J92" s="5" t="s">
+      <c r="J92" s="4" t="s">
         <v>588</v>
       </c>
-      <c r="K92" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L92" s="5">
+      <c r="K92" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L92" s="4">
         <v>8.9998245239257795E-3</v>
       </c>
     </row>
@@ -11742,40 +11723,40 @@
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A94" s="5" t="s">
+      <c r="A94" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="4">
         <v>0.17995262100000001</v>
       </c>
-      <c r="D94" s="5" t="s">
+      <c r="D94" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="E94" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F94" s="5">
+      <c r="E94" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F94" s="4">
         <v>1.19786262512207E-2</v>
       </c>
-      <c r="G94" s="5" t="s">
+      <c r="G94" s="4" t="s">
         <v>339</v>
       </c>
-      <c r="H94" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I94" s="5">
+      <c r="H94" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I94" s="4">
         <v>51.831717014312702</v>
       </c>
-      <c r="J94" s="5" t="s">
+      <c r="J94" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="K94" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L94" s="5">
+      <c r="K94" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L94" s="4">
         <v>1.02066993713378E-2</v>
       </c>
     </row>
@@ -11818,40 +11799,40 @@
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A96" s="5" t="s">
+      <c r="A96" s="4" t="s">
         <v>100</v>
       </c>
-      <c r="B96" s="5" t="s">
+      <c r="B96" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C96" s="5">
+      <c r="C96" s="4">
         <v>0.25074958800000002</v>
       </c>
-      <c r="D96" s="5" t="s">
+      <c r="D96" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="E96" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F96" s="5">
+      <c r="E96" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F96" s="4">
         <v>1.8818616867065398E-2</v>
       </c>
-      <c r="G96" s="5" t="s">
+      <c r="G96" s="4" t="s">
         <v>341</v>
       </c>
-      <c r="H96" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I96" s="5">
+      <c r="H96" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I96" s="4">
         <v>55.147148132324197</v>
       </c>
-      <c r="J96" s="5" t="s">
+      <c r="J96" s="4" t="s">
         <v>592</v>
       </c>
-      <c r="K96" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L96" s="5">
+      <c r="K96" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L96" s="4">
         <v>2.0788192749023399E-2</v>
       </c>
     </row>
@@ -11894,40 +11875,40 @@
       </c>
     </row>
     <row r="98" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A98" s="5" t="s">
+      <c r="A98" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B98" s="5" t="s">
+      <c r="B98" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C98" s="5">
+      <c r="C98" s="4">
         <v>0.24771141999999999</v>
       </c>
-      <c r="D98" s="5" t="s">
+      <c r="D98" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="E98" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F98" s="5">
+      <c r="E98" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F98" s="4">
         <v>2.0198583602905201E-2</v>
       </c>
-      <c r="G98" s="5" t="s">
+      <c r="G98" s="4" t="s">
         <v>343</v>
       </c>
-      <c r="H98" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I98" s="5">
+      <c r="H98" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I98" s="4">
         <v>55.295664548873901</v>
       </c>
-      <c r="J98" s="5" t="s">
+      <c r="J98" s="4" t="s">
         <v>594</v>
       </c>
-      <c r="K98" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L98" s="5">
+      <c r="K98" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L98" s="4">
         <v>2.0284652709960899E-2</v>
       </c>
     </row>
@@ -11970,40 +11951,40 @@
       </c>
     </row>
     <row r="100" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A100" s="5" t="s">
+      <c r="A100" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="B100" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C100" s="5">
+      <c r="B100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C100" s="4">
         <v>0.21818733200000001</v>
       </c>
-      <c r="D100" s="5" t="s">
+      <c r="D100" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="E100" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F100" s="5">
+      <c r="E100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F100" s="4">
         <v>1.46019458770751E-2</v>
       </c>
-      <c r="G100" s="5" t="s">
+      <c r="G100" s="4" t="s">
         <v>345</v>
       </c>
-      <c r="H100" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I100" s="5">
+      <c r="H100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I100" s="4">
         <v>3.04007530212402E-2</v>
       </c>
-      <c r="J100" s="5" t="s">
+      <c r="J100" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="K100" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L100" s="5">
+      <c r="K100" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L100" s="4">
         <v>2.05814838409423E-2</v>
       </c>
     </row>
@@ -12046,40 +12027,40 @@
       </c>
     </row>
     <row r="102" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A102" s="5" t="s">
+      <c r="A102" s="4" t="s">
         <v>106</v>
       </c>
-      <c r="B102" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C102" s="5">
+      <c r="B102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C102" s="4">
         <v>0.14196920399999999</v>
       </c>
-      <c r="D102" s="5" t="s">
+      <c r="D102" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="E102" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F102" s="5">
+      <c r="E102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F102" s="4">
         <v>1.42357349395751E-2</v>
       </c>
-      <c r="G102" s="5" t="s">
+      <c r="G102" s="4" t="s">
         <v>347</v>
       </c>
-      <c r="H102" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I102" s="5">
+      <c r="H102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I102" s="4">
         <v>1.6304492950439401E-2</v>
       </c>
-      <c r="J102" s="5" t="s">
+      <c r="J102" s="4" t="s">
         <v>598</v>
       </c>
-      <c r="K102" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L102" s="5">
+      <c r="K102" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L102" s="4">
         <v>2.67865657806396E-2</v>
       </c>
     </row>
@@ -12122,40 +12103,40 @@
       </c>
     </row>
     <row r="104" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A104" s="5" t="s">
+      <c r="A104" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="B104" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C104" s="5">
+      <c r="B104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C104" s="4">
         <v>0.51676321000000003</v>
       </c>
-      <c r="D104" s="5" t="s">
+      <c r="D104" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="E104" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F104" s="5">
+      <c r="E104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F104" s="4">
         <v>1.7321586608886701E-2</v>
       </c>
-      <c r="G104" s="5" t="s">
+      <c r="G104" s="4" t="s">
         <v>349</v>
       </c>
-      <c r="H104" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I104" s="5">
+      <c r="H104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I104" s="4">
         <v>3.5856962203979402E-2</v>
       </c>
-      <c r="J104" s="5" t="s">
+      <c r="J104" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="K104" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L104" s="5">
+      <c r="K104" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L104" s="4">
         <v>2.6749610900878899E-2</v>
       </c>
     </row>
@@ -12198,40 +12179,40 @@
       </c>
     </row>
     <row r="106" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A106" s="5" t="s">
+      <c r="A106" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="B106" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C106" s="5">
+      <c r="B106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C106" s="4">
         <v>0.21872091299999999</v>
       </c>
-      <c r="D106" s="5" t="s">
+      <c r="D106" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="E106" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F106" s="5">
+      <c r="E106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F106" s="4">
         <v>1.8084764480590799E-2</v>
       </c>
-      <c r="G106" s="5" t="s">
+      <c r="G106" s="4" t="s">
         <v>351</v>
       </c>
-      <c r="H106" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I106" s="5">
+      <c r="H106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I106" s="4">
         <v>3.7520170211791902E-2</v>
       </c>
-      <c r="J106" s="5" t="s">
+      <c r="J106" s="4" t="s">
         <v>602</v>
       </c>
-      <c r="K106" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L106" s="5">
+      <c r="K106" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L106" s="4">
         <v>2.70564556121826E-2</v>
       </c>
     </row>
@@ -12274,40 +12255,40 @@
       </c>
     </row>
     <row r="108" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A108" s="5" t="s">
+      <c r="A108" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="B108" s="5" t="s">
+      <c r="B108" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C108" s="4">
         <v>0.17705464400000001</v>
       </c>
-      <c r="D108" s="5" t="s">
+      <c r="D108" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="E108" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F108" s="5">
+      <c r="E108" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F108" s="4">
         <v>1.07629299163818E-2</v>
       </c>
-      <c r="G108" s="5" t="s">
+      <c r="G108" s="4" t="s">
         <v>353</v>
       </c>
-      <c r="H108" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I108" s="5">
+      <c r="H108" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I108" s="4">
         <v>6.2055587768554601E-3</v>
       </c>
-      <c r="J108" s="5" t="s">
+      <c r="J108" s="4" t="s">
         <v>604</v>
       </c>
-      <c r="K108" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L108" s="5">
+      <c r="K108" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L108" s="4">
         <v>1.05884075164794E-2</v>
       </c>
     </row>
@@ -12350,40 +12331,40 @@
       </c>
     </row>
     <row r="110" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A110" s="5" t="s">
+      <c r="A110" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B110" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C110" s="5">
+      <c r="B110" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C110" s="4">
         <v>0.51455783799999999</v>
       </c>
-      <c r="D110" s="5" t="s">
+      <c r="D110" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="E110" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F110" s="5">
+      <c r="E110" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F110" s="4">
         <v>1.69599056243896E-2</v>
       </c>
-      <c r="G110" s="5" t="s">
+      <c r="G110" s="4" t="s">
         <v>355</v>
       </c>
-      <c r="H110" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I110" s="5">
+      <c r="H110" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I110" s="4">
         <v>54.881767749786299</v>
       </c>
-      <c r="J110" s="5" t="s">
+      <c r="J110" s="4" t="s">
         <v>606</v>
       </c>
-      <c r="K110" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L110" s="5">
+      <c r="K110" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L110" s="4">
         <v>2.3982763290405201E-2</v>
       </c>
     </row>
@@ -12426,40 +12407,40 @@
       </c>
     </row>
     <row r="112" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A112" s="5" t="s">
+      <c r="A112" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="B112" s="5" t="s">
+      <c r="B112" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C112" s="5">
+      <c r="C112" s="4">
         <v>0.17127442400000001</v>
       </c>
-      <c r="D112" s="5" t="s">
+      <c r="D112" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="E112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F112" s="5">
+      <c r="E112" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F112" s="4">
         <v>1.0094165802001899E-2</v>
       </c>
-      <c r="G112" s="5" t="s">
+      <c r="G112" s="4" t="s">
         <v>357</v>
       </c>
-      <c r="H112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I112" s="5">
+      <c r="H112" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I112" s="4">
         <v>6.2487125396728498E-3</v>
       </c>
-      <c r="J112" s="5" t="s">
+      <c r="J112" s="4" t="s">
         <v>608</v>
       </c>
-      <c r="K112" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L112" s="5">
+      <c r="K112" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L112" s="4">
         <v>1.13670825958251E-2</v>
       </c>
     </row>
@@ -12502,40 +12483,40 @@
       </c>
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A114" s="5" t="s">
+      <c r="A114" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="B114" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C114" s="5">
+      <c r="B114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C114" s="4">
         <v>0.37490177200000002</v>
       </c>
-      <c r="D114" s="5" t="s">
+      <c r="D114" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="E114" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F114" s="5">
+      <c r="E114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F114" s="4">
         <v>1.1918783187866201E-2</v>
       </c>
-      <c r="G114" s="5" t="s">
+      <c r="G114" s="4" t="s">
         <v>359</v>
       </c>
-      <c r="H114" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I114" s="5">
+      <c r="H114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I114" s="4">
         <v>1.48563385009765E-2</v>
       </c>
-      <c r="J114" s="5" t="s">
+      <c r="J114" s="4" t="s">
         <v>610</v>
       </c>
-      <c r="K114" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L114" s="5">
+      <c r="K114" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L114" s="4">
         <v>1.7786979675292899E-2</v>
       </c>
     </row>
@@ -12578,40 +12559,40 @@
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A116" s="5" t="s">
+      <c r="A116" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="B116" s="5" t="s">
+      <c r="B116" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C116" s="5">
+      <c r="C116" s="4">
         <v>0.16797137300000001</v>
       </c>
-      <c r="D116" s="5" t="s">
+      <c r="D116" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="E116" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F116" s="5">
+      <c r="E116" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F116" s="4">
         <v>1.06663703918457E-2</v>
       </c>
-      <c r="G116" s="5" t="s">
+      <c r="G116" s="4" t="s">
         <v>361</v>
       </c>
-      <c r="H116" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I116" s="5">
+      <c r="H116" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I116" s="4">
         <v>51.778589487075799</v>
       </c>
-      <c r="J116" s="5" t="s">
+      <c r="J116" s="4" t="s">
         <v>612</v>
       </c>
-      <c r="K116" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L116" s="5">
+      <c r="K116" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L116" s="4">
         <v>1.10623836517333E-2</v>
       </c>
     </row>
@@ -12654,40 +12635,40 @@
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A118" s="5" t="s">
+      <c r="A118" s="4" t="s">
         <v>122</v>
       </c>
-      <c r="B118" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C118" s="5">
+      <c r="B118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C118" s="4">
         <v>0.367304564</v>
       </c>
-      <c r="D118" s="5" t="s">
+      <c r="D118" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="E118" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F118" s="5">
+      <c r="E118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F118" s="4">
         <v>1.1106729507446201E-2</v>
       </c>
-      <c r="G118" s="5" t="s">
+      <c r="G118" s="4" t="s">
         <v>363</v>
       </c>
-      <c r="H118" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I118" s="5">
+      <c r="H118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I118" s="4">
         <v>1.5968799591064401E-2</v>
       </c>
-      <c r="J118" s="5" t="s">
+      <c r="J118" s="4" t="s">
         <v>614</v>
       </c>
-      <c r="K118" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L118" s="5">
+      <c r="K118" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L118" s="4">
         <v>1.7588376998901301E-2</v>
       </c>
     </row>
@@ -12730,40 +12711,40 @@
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A120" s="5" t="s">
+      <c r="A120" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="B120" s="5" t="s">
+      <c r="B120" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C120" s="5">
+      <c r="C120" s="4">
         <v>0.247147322</v>
       </c>
-      <c r="D120" s="5" t="s">
+      <c r="D120" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="E120" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F120" s="5">
+      <c r="E120" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F120" s="4">
         <v>2.00438499450683E-2</v>
       </c>
-      <c r="G120" s="5" t="s">
+      <c r="G120" s="4" t="s">
         <v>365</v>
       </c>
-      <c r="H120" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I120" s="5">
+      <c r="H120" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I120" s="4">
         <v>55.634057998657198</v>
       </c>
-      <c r="J120" s="5" t="s">
+      <c r="J120" s="4" t="s">
         <v>616</v>
       </c>
-      <c r="K120" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L120" s="5">
+      <c r="K120" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L120" s="4">
         <v>2.0206451416015601E-2</v>
       </c>
     </row>
@@ -12806,40 +12787,40 @@
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A122" s="5" t="s">
+      <c r="A122" s="4" t="s">
         <v>126</v>
       </c>
-      <c r="B122" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C122" s="5">
+      <c r="B122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C122" s="4">
         <v>0.34815359099999998</v>
       </c>
-      <c r="D122" s="5" t="s">
+      <c r="D122" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="E122" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F122" s="5">
+      <c r="E122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F122" s="4">
         <v>9.41824913024902E-3</v>
       </c>
-      <c r="G122" s="5" t="s">
+      <c r="G122" s="4" t="s">
         <v>367</v>
       </c>
-      <c r="H122" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I122" s="5">
+      <c r="H122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I122" s="4">
         <v>1.3995409011840799E-2</v>
       </c>
-      <c r="J122" s="5" t="s">
+      <c r="J122" s="4" t="s">
         <v>618</v>
       </c>
-      <c r="K122" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L122" s="5">
+      <c r="K122" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L122" s="4">
         <v>1.5785217285156201E-2</v>
       </c>
     </row>
@@ -12882,40 +12863,40 @@
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A124" s="5" t="s">
+      <c r="A124" s="4" t="s">
         <v>128</v>
       </c>
-      <c r="B124" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C124" s="5">
+      <c r="B124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C124" s="4">
         <v>0.36348986599999999</v>
       </c>
-      <c r="D124" s="5" t="s">
+      <c r="D124" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="E124" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F124" s="5">
+      <c r="E124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F124" s="4">
         <v>1.06801986694335E-2</v>
       </c>
-      <c r="G124" s="5" t="s">
+      <c r="G124" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="H124" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I124" s="5">
+      <c r="H124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I124" s="4">
         <v>1.47624015808105E-2</v>
       </c>
-      <c r="J124" s="5" t="s">
+      <c r="J124" s="4" t="s">
         <v>620</v>
       </c>
-      <c r="K124" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L124" s="5">
+      <c r="K124" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L124" s="4">
         <v>1.6087770462036102E-2</v>
       </c>
     </row>
@@ -12958,40 +12939,40 @@
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A126" s="5" t="s">
+      <c r="A126" s="4" t="s">
         <v>130</v>
       </c>
-      <c r="B126" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C126" s="5">
+      <c r="B126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C126" s="4">
         <v>0.34684705700000001</v>
       </c>
-      <c r="D126" s="5" t="s">
+      <c r="D126" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="E126" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F126" s="5">
+      <c r="E126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F126" s="4">
         <v>1.0850667953491201E-2</v>
       </c>
-      <c r="G126" s="5" t="s">
+      <c r="G126" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="H126" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I126" s="5">
+      <c r="H126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I126" s="4">
         <v>1.46448612213134E-2</v>
       </c>
-      <c r="J126" s="5" t="s">
+      <c r="J126" s="4" t="s">
         <v>622</v>
       </c>
-      <c r="K126" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L126" s="5">
+      <c r="K126" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L126" s="4">
         <v>1.57418251037597E-2</v>
       </c>
     </row>
@@ -13034,40 +13015,40 @@
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A128" s="5" t="s">
+      <c r="A128" s="4" t="s">
         <v>132</v>
       </c>
-      <c r="B128" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C128" s="5">
+      <c r="B128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C128" s="4">
         <v>0.35608339300000003</v>
       </c>
-      <c r="D128" s="5" t="s">
+      <c r="D128" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="E128" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F128" s="5">
+      <c r="E128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F128" s="4">
         <v>9.2265605926513602E-3</v>
       </c>
-      <c r="G128" s="5" t="s">
+      <c r="G128" s="4" t="s">
         <v>373</v>
       </c>
-      <c r="H128" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I128" s="5">
+      <c r="H128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I128" s="4">
         <v>1.53450965881347E-2</v>
       </c>
-      <c r="J128" s="5" t="s">
+      <c r="J128" s="4" t="s">
         <v>624</v>
       </c>
-      <c r="K128" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L128" s="5">
+      <c r="K128" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L128" s="4">
         <v>1.54721736907958E-2</v>
       </c>
     </row>
@@ -13110,40 +13091,40 @@
       </c>
     </row>
     <row r="130" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A130" s="5" t="s">
+      <c r="A130" s="4" t="s">
         <v>134</v>
       </c>
-      <c r="B130" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C130" s="5">
+      <c r="B130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C130" s="4">
         <v>0.47153735200000002</v>
       </c>
-      <c r="D130" s="5" t="s">
+      <c r="D130" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="E130" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F130" s="5">
+      <c r="E130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F130" s="4">
         <v>1.0214567184448201E-2</v>
       </c>
-      <c r="G130" s="5" t="s">
+      <c r="G130" s="4" t="s">
         <v>375</v>
       </c>
-      <c r="H130" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I130" s="5">
+      <c r="H130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I130" s="4">
         <v>1.4728069305419899E-2</v>
       </c>
-      <c r="J130" s="5" t="s">
+      <c r="J130" s="4" t="s">
         <v>626</v>
       </c>
-      <c r="K130" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L130" s="5">
+      <c r="K130" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L130" s="4">
         <v>1.5936613082885701E-2</v>
       </c>
     </row>
@@ -13186,40 +13167,40 @@
       </c>
     </row>
     <row r="132" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A132" s="5" t="s">
+      <c r="A132" s="4" t="s">
         <v>136</v>
       </c>
-      <c r="B132" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C132" s="5">
+      <c r="B132" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C132" s="4">
         <v>0.45425343499999998</v>
       </c>
-      <c r="D132" s="5" t="s">
+      <c r="D132" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="E132" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F132" s="5">
+      <c r="E132" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F132" s="4">
         <v>1.01194381713867E-2</v>
       </c>
-      <c r="G132" s="5" t="s">
+      <c r="G132" s="4" t="s">
         <v>377</v>
       </c>
-      <c r="H132" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I132" s="5">
+      <c r="H132" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I132" s="4">
         <v>1.4682292938232399E-2</v>
       </c>
-      <c r="J132" s="5" t="s">
+      <c r="J132" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="K132" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L132" s="5">
+      <c r="K132" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L132" s="4">
         <v>1.56540870666503E-2</v>
       </c>
     </row>
@@ -13262,40 +13243,40 @@
       </c>
     </row>
     <row r="134" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A134" s="5" t="s">
+      <c r="A134" s="4" t="s">
         <v>138</v>
       </c>
-      <c r="B134" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C134" s="5">
+      <c r="B134" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C134" s="4">
         <v>0.35852551500000002</v>
       </c>
-      <c r="D134" s="5" t="s">
+      <c r="D134" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="E134" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F134" s="5">
+      <c r="E134" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F134" s="4">
         <v>1.08568668365478E-2</v>
       </c>
-      <c r="G134" s="5" t="s">
+      <c r="G134" s="4" t="s">
         <v>379</v>
       </c>
-      <c r="H134" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I134" s="5">
+      <c r="H134" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I134" s="4">
         <v>1.55131816864013E-2</v>
       </c>
-      <c r="J134" s="5" t="s">
+      <c r="J134" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="K134" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L134" s="5">
+      <c r="K134" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L134" s="4">
         <v>1.5791177749633699E-2</v>
       </c>
     </row>
@@ -13338,40 +13319,40 @@
       </c>
     </row>
     <row r="136" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A136" s="5" t="s">
+      <c r="A136" s="4" t="s">
         <v>140</v>
       </c>
-      <c r="B136" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C136" s="5">
+      <c r="B136" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C136" s="4">
         <v>0.46444869</v>
       </c>
-      <c r="D136" s="5" t="s">
+      <c r="D136" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="E136" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F136" s="5">
+      <c r="E136" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F136" s="4">
         <v>9.8056793212890608E-3</v>
       </c>
-      <c r="G136" s="5" t="s">
+      <c r="G136" s="4" t="s">
         <v>381</v>
       </c>
-      <c r="H136" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I136" s="5">
+      <c r="H136" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I136" s="4">
         <v>1.4964342117309499E-2</v>
       </c>
-      <c r="J136" s="5" t="s">
+      <c r="J136" s="4" t="s">
         <v>632</v>
       </c>
-      <c r="K136" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L136" s="5">
+      <c r="K136" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L136" s="4">
         <v>1.6247749328613201E-2</v>
       </c>
     </row>
@@ -13414,40 +13395,40 @@
       </c>
     </row>
     <row r="138" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A138" s="5" t="s">
+      <c r="A138" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="B138" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C138" s="5">
+      <c r="B138" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C138" s="4">
         <v>0.47768902800000002</v>
       </c>
-      <c r="D138" s="5" t="s">
+      <c r="D138" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="E138" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F138" s="5">
+      <c r="E138" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F138" s="4">
         <v>1.09100341796875E-2</v>
       </c>
-      <c r="G138" s="5" t="s">
+      <c r="G138" s="4" t="s">
         <v>383</v>
       </c>
-      <c r="H138" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I138" s="5">
+      <c r="H138" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I138" s="4">
         <v>1.45554542541503E-2</v>
       </c>
-      <c r="J138" s="5" t="s">
+      <c r="J138" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="K138" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L138" s="5">
+      <c r="K138" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L138" s="4">
         <v>1.58987045288085E-2</v>
       </c>
     </row>
@@ -13490,40 +13471,40 @@
       </c>
     </row>
     <row r="140" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A140" s="5" t="s">
+      <c r="A140" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B140" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C140" s="5">
+      <c r="B140" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C140" s="4">
         <v>0.48166918800000003</v>
       </c>
-      <c r="D140" s="5" t="s">
+      <c r="D140" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="E140" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F140" s="5">
+      <c r="E140" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F140" s="4">
         <v>1.3637304306030201E-2</v>
       </c>
-      <c r="G140" s="5" t="s">
+      <c r="G140" s="4" t="s">
         <v>385</v>
       </c>
-      <c r="H140" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I140" s="5">
+      <c r="H140" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I140" s="4">
         <v>1.6377687454223602E-2</v>
       </c>
-      <c r="J140" s="5" t="s">
+      <c r="J140" s="4" t="s">
         <v>636</v>
       </c>
-      <c r="K140" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L140" s="5">
+      <c r="K140" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L140" s="4">
         <v>1.9095420837402299E-2</v>
       </c>
     </row>
@@ -13566,40 +13547,40 @@
       </c>
     </row>
     <row r="142" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A142" s="5" t="s">
+      <c r="A142" s="4" t="s">
         <v>146</v>
       </c>
-      <c r="B142" s="5" t="s">
+      <c r="B142" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C142" s="5">
+      <c r="C142" s="4">
         <v>0.171499968</v>
       </c>
-      <c r="D142" s="5" t="s">
+      <c r="D142" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="E142" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F142" s="5">
+      <c r="E142" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F142" s="4">
         <v>9.4113349914550695E-3</v>
       </c>
-      <c r="G142" s="5" t="s">
+      <c r="G142" s="4" t="s">
         <v>387</v>
       </c>
-      <c r="H142" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I142" s="5">
+      <c r="H142" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I142" s="4">
         <v>6.3109397888183498E-3</v>
       </c>
-      <c r="J142" s="5" t="s">
+      <c r="J142" s="4" t="s">
         <v>638</v>
       </c>
-      <c r="K142" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L142" s="5">
+      <c r="K142" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L142" s="4">
         <v>1.1859416961669899E-2</v>
       </c>
     </row>
@@ -13642,40 +13623,40 @@
       </c>
     </row>
     <row r="144" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A144" s="5" t="s">
+      <c r="A144" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B144" s="5" t="s">
+      <c r="B144" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C144" s="5">
+      <c r="C144" s="4">
         <v>0.17306637799999999</v>
       </c>
-      <c r="D144" s="5" t="s">
+      <c r="D144" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="E144" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F144" s="5">
+      <c r="E144" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F144" s="4">
         <v>1.0796070098876899E-2</v>
       </c>
-      <c r="G144" s="5" t="s">
+      <c r="G144" s="4" t="s">
         <v>389</v>
       </c>
-      <c r="H144" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I144" s="5">
+      <c r="H144" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I144" s="4">
         <v>51.5318858623504</v>
       </c>
-      <c r="J144" s="5" t="s">
+      <c r="J144" s="4" t="s">
         <v>640</v>
       </c>
-      <c r="K144" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L144" s="5">
+      <c r="K144" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L144" s="4">
         <v>1.11839771270751E-2</v>
       </c>
     </row>
@@ -13718,40 +13699,40 @@
       </c>
     </row>
     <row r="146" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A146" s="5" t="s">
+      <c r="A146" s="4" t="s">
         <v>150</v>
       </c>
-      <c r="B146" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C146" s="5">
+      <c r="B146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C146" s="4">
         <v>0.34143090199999998</v>
       </c>
-      <c r="D146" s="5" t="s">
+      <c r="D146" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="E146" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F146" s="5">
+      <c r="E146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F146" s="4">
         <v>9.3653202056884696E-3</v>
       </c>
-      <c r="G146" s="5" t="s">
+      <c r="G146" s="4" t="s">
         <v>391</v>
       </c>
-      <c r="H146" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I146" s="5">
+      <c r="H146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I146" s="4">
         <v>1.3647317886352499E-2</v>
       </c>
-      <c r="J146" s="5" t="s">
+      <c r="J146" s="4" t="s">
         <v>642</v>
       </c>
-      <c r="K146" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L146" s="5">
+      <c r="K146" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L146" s="4">
         <v>1.5257120132446201E-2</v>
       </c>
     </row>
@@ -13794,40 +13775,40 @@
       </c>
     </row>
     <row r="148" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A148" s="5" t="s">
+      <c r="A148" s="4" t="s">
         <v>152</v>
       </c>
-      <c r="B148" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C148" s="5">
+      <c r="B148" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C148" s="4">
         <v>0.36128663999999999</v>
       </c>
-      <c r="D148" s="5" t="s">
+      <c r="D148" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="E148" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F148" s="5">
+      <c r="E148" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F148" s="4">
         <v>1.01723670959472E-2</v>
       </c>
-      <c r="G148" s="5" t="s">
+      <c r="G148" s="4" t="s">
         <v>393</v>
       </c>
-      <c r="H148" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I148" s="5">
+      <c r="H148" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I148" s="4">
         <v>1.4146327972412101E-2</v>
       </c>
-      <c r="J148" s="5" t="s">
+      <c r="J148" s="4" t="s">
         <v>644</v>
       </c>
-      <c r="K148" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L148" s="5">
+      <c r="K148" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L148" s="4">
         <v>1.5687942504882799E-2</v>
       </c>
     </row>
@@ -13870,40 +13851,40 @@
       </c>
     </row>
     <row r="150" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A150" s="5" t="s">
+      <c r="A150" s="4" t="s">
         <v>154</v>
       </c>
-      <c r="B150" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C150" s="5">
+      <c r="B150" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C150" s="4">
         <v>0.40009808499999999</v>
       </c>
-      <c r="D150" s="5" t="s">
+      <c r="D150" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="E150" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F150" s="5">
+      <c r="E150" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F150" s="4">
         <v>1.65457725524902E-2</v>
       </c>
-      <c r="G150" s="5" t="s">
+      <c r="G150" s="4" t="s">
         <v>395</v>
       </c>
-      <c r="H150" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I150" s="5">
+      <c r="H150" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I150" s="4">
         <v>54.906613826751702</v>
       </c>
-      <c r="J150" s="5" t="s">
+      <c r="J150" s="4" t="s">
         <v>646</v>
       </c>
-      <c r="K150" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L150" s="5">
+      <c r="K150" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L150" s="4">
         <v>2.34160423278808E-2</v>
       </c>
     </row>
@@ -13946,40 +13927,40 @@
       </c>
     </row>
     <row r="152" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A152" s="5" t="s">
+      <c r="A152" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="B152" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C152" s="5">
+      <c r="B152" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C152" s="4">
         <v>0.35350227400000001</v>
       </c>
-      <c r="D152" s="5" t="s">
+      <c r="D152" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="E152" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F152" s="5">
+      <c r="E152" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F152" s="4">
         <v>1.10881328582763E-2</v>
       </c>
-      <c r="G152" s="5" t="s">
+      <c r="G152" s="4" t="s">
         <v>397</v>
       </c>
-      <c r="H152" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I152" s="5">
+      <c r="H152" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I152" s="4">
         <v>1.4868259429931601E-2</v>
       </c>
-      <c r="J152" s="5" t="s">
+      <c r="J152" s="4" t="s">
         <v>648</v>
       </c>
-      <c r="K152" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L152" s="5">
+      <c r="K152" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L152" s="4">
         <v>1.6492605209350499E-2</v>
       </c>
     </row>
@@ -14022,40 +14003,40 @@
       </c>
     </row>
     <row r="154" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A154" s="5" t="s">
+      <c r="A154" s="4" t="s">
         <v>158</v>
       </c>
-      <c r="B154" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C154" s="5">
+      <c r="B154" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C154" s="4">
         <v>0.353208303</v>
       </c>
-      <c r="D154" s="5" t="s">
+      <c r="D154" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="E154" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F154" s="5">
+      <c r="E154" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F154" s="4">
         <v>1.21223926544189E-2</v>
       </c>
-      <c r="G154" s="5" t="s">
+      <c r="G154" s="4" t="s">
         <v>399</v>
       </c>
-      <c r="H154" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I154" s="5">
+      <c r="H154" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I154" s="4">
         <v>1.6108274459838801E-2</v>
       </c>
-      <c r="J154" s="5" t="s">
+      <c r="J154" s="4" t="s">
         <v>650</v>
       </c>
-      <c r="K154" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L154" s="5">
+      <c r="K154" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L154" s="4">
         <v>1.6212463378906201E-2</v>
       </c>
     </row>
@@ -14098,40 +14079,40 @@
       </c>
     </row>
     <row r="156" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A156" s="5" t="s">
+      <c r="A156" s="4" t="s">
         <v>160</v>
       </c>
-      <c r="B156" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C156" s="5">
+      <c r="B156" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C156" s="4">
         <v>0.37076234800000002</v>
       </c>
-      <c r="D156" s="5" t="s">
+      <c r="D156" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="E156" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F156" s="5">
+      <c r="E156" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F156" s="4">
         <v>1.11033916473388E-2</v>
       </c>
-      <c r="G156" s="5" t="s">
+      <c r="G156" s="4" t="s">
         <v>401</v>
       </c>
-      <c r="H156" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I156" s="5">
+      <c r="H156" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I156" s="4">
         <v>1.35178565979003E-2</v>
       </c>
-      <c r="J156" s="5" t="s">
+      <c r="J156" s="4" t="s">
         <v>652</v>
       </c>
-      <c r="K156" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L156" s="5">
+      <c r="K156" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L156" s="4">
         <v>1.5570402145385701E-2</v>
       </c>
     </row>
@@ -14174,40 +14155,40 @@
       </c>
     </row>
     <row r="158" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A158" s="5" t="s">
+      <c r="A158" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B158" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C158" s="5">
+      <c r="B158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C158" s="4">
         <v>0.34214568099999998</v>
       </c>
-      <c r="D158" s="5" t="s">
+      <c r="D158" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="E158" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F158" s="5">
+      <c r="E158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F158" s="4">
         <v>1.2246370315551701E-2</v>
       </c>
-      <c r="G158" s="5" t="s">
+      <c r="G158" s="4" t="s">
         <v>403</v>
       </c>
-      <c r="H158" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I158" s="5">
+      <c r="H158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I158" s="4">
         <v>1.52359008789062E-2</v>
       </c>
-      <c r="J158" s="5" t="s">
+      <c r="J158" s="4" t="s">
         <v>654</v>
       </c>
-      <c r="K158" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L158" s="5">
+      <c r="K158" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L158" s="4">
         <v>1.6328334808349599E-2</v>
       </c>
     </row>
@@ -14250,40 +14231,40 @@
       </c>
     </row>
     <row r="160" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A160" s="5" t="s">
+      <c r="A160" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="B160" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C160" s="5">
+      <c r="B160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C160" s="4">
         <v>0.33524799300000002</v>
       </c>
-      <c r="D160" s="5" t="s">
+      <c r="D160" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="E160" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F160" s="5">
+      <c r="E160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F160" s="4">
         <v>1.14259719848632E-2</v>
       </c>
-      <c r="G160" s="5" t="s">
+      <c r="G160" s="4" t="s">
         <v>405</v>
       </c>
-      <c r="H160" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I160" s="5">
+      <c r="H160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I160" s="4">
         <v>1.52969360351562E-2</v>
       </c>
-      <c r="J160" s="5" t="s">
+      <c r="J160" s="4" t="s">
         <v>656</v>
       </c>
-      <c r="K160" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L160" s="5">
+      <c r="K160" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L160" s="4">
         <v>1.6744613647460899E-2</v>
       </c>
     </row>
@@ -14326,40 +14307,40 @@
       </c>
     </row>
     <row r="162" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A162" s="5" t="s">
+      <c r="A162" s="4" t="s">
         <v>166</v>
       </c>
-      <c r="B162" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C162" s="5">
+      <c r="B162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C162" s="4">
         <v>0.35958957699999999</v>
       </c>
-      <c r="D162" s="5" t="s">
+      <c r="D162" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="E162" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F162" s="5">
+      <c r="E162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F162" s="4">
         <v>1.1050939559936499E-2</v>
       </c>
-      <c r="G162" s="5" t="s">
+      <c r="G162" s="4" t="s">
         <v>407</v>
       </c>
-      <c r="H162" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I162" s="5">
+      <c r="H162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I162" s="4">
         <v>1.50506496429443E-2</v>
       </c>
-      <c r="J162" s="5" t="s">
+      <c r="J162" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="K162" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L162" s="5">
+      <c r="K162" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L162" s="4">
         <v>1.6557455062866201E-2</v>
       </c>
     </row>
@@ -14402,40 +14383,40 @@
       </c>
     </row>
     <row r="164" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A164" s="5" t="s">
+      <c r="A164" s="4" t="s">
         <v>168</v>
       </c>
-      <c r="B164" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C164" s="5">
+      <c r="B164" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C164" s="4">
         <v>0.28739976900000003</v>
       </c>
-      <c r="D164" s="5" t="s">
+      <c r="D164" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="E164" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F164" s="5">
+      <c r="E164" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F164" s="4">
         <v>1.0941743850707999E-2</v>
       </c>
-      <c r="G164" s="5" t="s">
+      <c r="G164" s="4" t="s">
         <v>409</v>
       </c>
-      <c r="H164" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I164" s="5">
+      <c r="H164" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I164" s="4">
         <v>55.991229057311998</v>
       </c>
-      <c r="J164" s="5" t="s">
+      <c r="J164" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="K164" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L164" s="5">
+      <c r="K164" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L164" s="4">
         <v>1.8865346908569301E-2</v>
       </c>
     </row>
@@ -14478,40 +14459,40 @@
       </c>
     </row>
     <row r="166" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A166" s="5" t="s">
+      <c r="A166" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="B166" s="5" t="s">
+      <c r="B166" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C166" s="5">
+      <c r="C166" s="4">
         <v>0.49367165600000001</v>
       </c>
-      <c r="D166" s="5" t="s">
+      <c r="D166" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="E166" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F166" s="5">
+      <c r="E166" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F166" s="4">
         <v>4.5522928237914997E-2</v>
       </c>
-      <c r="G166" s="5" t="s">
+      <c r="G166" s="4" t="s">
         <v>411</v>
       </c>
-      <c r="H166" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I166" s="5">
+      <c r="H166" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I166" s="4">
         <v>53.545220851898101</v>
       </c>
-      <c r="J166" s="5" t="s">
+      <c r="J166" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="K166" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L166" s="5">
+      <c r="K166" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L166" s="4">
         <v>4.7327518463134703E-2</v>
       </c>
     </row>
@@ -14554,40 +14535,40 @@
       </c>
     </row>
     <row r="168" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A168" s="5" t="s">
+      <c r="A168" s="4" t="s">
         <v>172</v>
       </c>
-      <c r="B168" s="5" t="s">
+      <c r="B168" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C168" s="5">
+      <c r="C168" s="4">
         <v>14.993003849999999</v>
       </c>
-      <c r="D168" s="5" t="s">
+      <c r="D168" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="E168" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F168" s="5">
+      <c r="E168" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F168" s="4">
         <v>0.893929243087768</v>
       </c>
-      <c r="G168" s="5" t="s">
+      <c r="G168" s="4" t="s">
         <v>413</v>
       </c>
-      <c r="H168" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I168" s="5">
+      <c r="H168" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I168" s="4">
         <v>53.025864124298003</v>
       </c>
-      <c r="J168" s="5" t="s">
+      <c r="J168" s="4" t="s">
         <v>664</v>
       </c>
-      <c r="K168" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L168" s="5">
+      <c r="K168" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L168" s="4">
         <v>0.93724679946899403</v>
       </c>
     </row>
@@ -14630,40 +14611,40 @@
       </c>
     </row>
     <row r="170" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A170" s="5" t="s">
+      <c r="A170" s="4" t="s">
         <v>174</v>
       </c>
-      <c r="B170" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C170" s="5">
+      <c r="B170" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C170" s="4">
         <v>11.229896310000001</v>
       </c>
-      <c r="D170" s="5" t="s">
+      <c r="D170" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="E170" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F170" s="5">
+      <c r="E170" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F170" s="4">
         <v>81.6706733703613</v>
       </c>
-      <c r="G170" s="5" t="s">
+      <c r="G170" s="4" t="s">
         <v>415</v>
       </c>
-      <c r="H170" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I170" s="5">
+      <c r="H170" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I170" s="4">
         <v>51.453446865081702</v>
       </c>
-      <c r="J170" s="5" t="s">
+      <c r="J170" s="4" t="s">
         <v>666</v>
       </c>
-      <c r="K170" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L170" s="5">
+      <c r="K170" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L170" s="4">
         <v>77.130455732345496</v>
       </c>
     </row>
@@ -14706,40 +14687,40 @@
       </c>
     </row>
     <row r="172" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A172" s="5" t="s">
+      <c r="A172" s="4" t="s">
         <v>176</v>
       </c>
-      <c r="B172" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C172" s="5">
+      <c r="B172" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C172" s="4">
         <v>50.81062841</v>
       </c>
-      <c r="D172" s="5" t="s">
+      <c r="D172" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="E172" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F172" s="5">
+      <c r="E172" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F172" s="4">
         <v>1.85542106628417E-2</v>
       </c>
-      <c r="G172" s="5" t="s">
+      <c r="G172" s="4" t="s">
         <v>417</v>
       </c>
-      <c r="H172" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I172" s="5">
+      <c r="H172" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I172" s="4">
         <v>0.40102791786193798</v>
       </c>
-      <c r="J172" s="5" t="s">
+      <c r="J172" s="4" t="s">
         <v>668</v>
       </c>
-      <c r="K172" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L172" s="5">
+      <c r="K172" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L172" s="4">
         <v>0.88915467262268</v>
       </c>
     </row>
@@ -14782,40 +14763,40 @@
       </c>
     </row>
     <row r="174" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A174" s="5" t="s">
+      <c r="A174" s="4" t="s">
         <v>178</v>
       </c>
-      <c r="B174" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C174" s="5">
+      <c r="B174" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C174" s="4">
         <v>51.609510419999999</v>
       </c>
-      <c r="D174" s="5" t="s">
+      <c r="D174" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="E174" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F174" s="5">
+      <c r="E174" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F174" s="4">
         <v>2.06284523010253E-2</v>
       </c>
-      <c r="G174" s="5" t="s">
+      <c r="G174" s="4" t="s">
         <v>419</v>
       </c>
-      <c r="H174" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I174" s="5">
+      <c r="H174" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I174" s="4">
         <v>0.23285984992980899</v>
       </c>
-      <c r="J174" s="5" t="s">
+      <c r="J174" s="4" t="s">
         <v>670</v>
       </c>
-      <c r="K174" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L174" s="5">
+      <c r="K174" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L174" s="4">
         <v>0.91698789596557595</v>
       </c>
     </row>
@@ -14858,40 +14839,40 @@
       </c>
     </row>
     <row r="176" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A176" s="5" t="s">
+      <c r="A176" s="4" t="s">
         <v>180</v>
       </c>
-      <c r="B176" s="5" t="s">
+      <c r="B176" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C176" s="5">
+      <c r="C176" s="4">
         <v>19.800553560000001</v>
       </c>
-      <c r="D176" s="5" t="s">
+      <c r="D176" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="E176" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F176" s="5">
+      <c r="E176" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F176" s="4">
         <v>0.58092975616455</v>
       </c>
-      <c r="G176" s="5" t="s">
+      <c r="G176" s="4" t="s">
         <v>421</v>
       </c>
-      <c r="H176" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I176" s="5">
+      <c r="H176" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I176" s="4">
         <v>51.487279176712001</v>
       </c>
-      <c r="J176" s="5" t="s">
+      <c r="J176" s="4" t="s">
         <v>672</v>
       </c>
-      <c r="K176" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L176" s="5">
+      <c r="K176" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L176" s="4">
         <v>0.58160829544067305</v>
       </c>
     </row>
@@ -14934,40 +14915,40 @@
       </c>
     </row>
     <row r="178" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A178" s="5" t="s">
+      <c r="A178" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="B178" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C178" s="5">
+      <c r="B178" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C178" s="4">
         <v>3.5504252909999998</v>
       </c>
-      <c r="D178" s="5" t="s">
+      <c r="D178" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="E178" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F178" s="5">
+      <c r="E178" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F178" s="4">
         <v>4.68277931213378E-2</v>
       </c>
-      <c r="G178" s="5" t="s">
+      <c r="G178" s="4" t="s">
         <v>423</v>
       </c>
-      <c r="H178" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I178" s="5">
+      <c r="H178" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I178" s="4">
         <v>51.7902734279632</v>
       </c>
-      <c r="J178" s="5" t="s">
+      <c r="J178" s="4" t="s">
         <v>674</v>
       </c>
-      <c r="K178" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L178" s="5">
+      <c r="K178" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L178" s="4">
         <v>6.2379598617553697E-2</v>
       </c>
     </row>
@@ -15010,40 +14991,40 @@
       </c>
     </row>
     <row r="180" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A180" s="5" t="s">
+      <c r="A180" s="4" t="s">
         <v>184</v>
       </c>
-      <c r="B180" s="5" t="s">
+      <c r="B180" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C180" s="5">
+      <c r="C180" s="4">
         <v>0.186239243</v>
       </c>
-      <c r="D180" s="5" t="s">
+      <c r="D180" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="E180" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F180" s="5">
+      <c r="E180" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F180" s="4">
         <v>7.46679306030273E-3</v>
       </c>
-      <c r="G180" s="5" t="s">
+      <c r="G180" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="H180" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I180" s="5">
+      <c r="H180" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I180" s="4">
         <v>4.4300556182861302E-3</v>
       </c>
-      <c r="J180" s="5" t="s">
+      <c r="J180" s="4" t="s">
         <v>676</v>
       </c>
-      <c r="K180" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L180" s="5">
+      <c r="K180" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L180" s="4">
         <v>7.7781677246093698E-3</v>
       </c>
     </row>
@@ -15086,40 +15067,40 @@
       </c>
     </row>
     <row r="182" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A182" s="5" t="s">
+      <c r="A182" s="4" t="s">
         <v>186</v>
       </c>
-      <c r="B182" s="5" t="s">
+      <c r="B182" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C182" s="5">
+      <c r="C182" s="4">
         <v>0.283760548</v>
       </c>
-      <c r="D182" s="5" t="s">
+      <c r="D182" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="E182" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F182" s="5">
+      <c r="E182" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F182" s="4">
         <v>4.5357465744018499E-2</v>
       </c>
-      <c r="G182" s="5" t="s">
+      <c r="G182" s="4" t="s">
         <v>427</v>
       </c>
-      <c r="H182" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I182" s="5">
+      <c r="H182" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I182" s="4">
         <v>51.246623039245598</v>
       </c>
-      <c r="J182" s="5" t="s">
+      <c r="J182" s="4" t="s">
         <v>678</v>
       </c>
-      <c r="K182" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L182" s="5">
+      <c r="K182" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L182" s="4">
         <v>4.5527458190917899E-2</v>
       </c>
     </row>
@@ -15162,40 +15143,40 @@
       </c>
     </row>
     <row r="184" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A184" s="5" t="s">
+      <c r="A184" s="4" t="s">
         <v>188</v>
       </c>
-      <c r="B184" s="5" t="s">
+      <c r="B184" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C184" s="5">
+      <c r="C184" s="4">
         <v>0.246244669</v>
       </c>
-      <c r="D184" s="5" t="s">
+      <c r="D184" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="E184" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F184" s="5">
+      <c r="E184" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F184" s="4">
         <v>1.87861919403076E-2</v>
       </c>
-      <c r="G184" s="5" t="s">
+      <c r="G184" s="4" t="s">
         <v>429</v>
       </c>
-      <c r="H184" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I184" s="5">
+      <c r="H184" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I184" s="4">
         <v>53.648635864257798</v>
       </c>
-      <c r="J184" s="5" t="s">
+      <c r="J184" s="4" t="s">
         <v>680</v>
       </c>
-      <c r="K184" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L184" s="5">
+      <c r="K184" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L184" s="4">
         <v>1.7657518386840799E-2</v>
       </c>
     </row>
@@ -15238,40 +15219,40 @@
       </c>
     </row>
     <row r="186" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A186" s="5" t="s">
+      <c r="A186" s="4" t="s">
         <v>190</v>
       </c>
-      <c r="B186" s="5" t="s">
+      <c r="B186" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C186" s="5">
+      <c r="C186" s="4">
         <v>0.49741196599999998</v>
       </c>
-      <c r="D186" s="5" t="s">
+      <c r="D186" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="E186" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F186" s="5">
+      <c r="E186" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F186" s="4">
         <v>4.5390844345092697E-2</v>
       </c>
-      <c r="G186" s="5" t="s">
+      <c r="G186" s="4" t="s">
         <v>431</v>
       </c>
-      <c r="H186" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I186" s="5">
+      <c r="H186" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I186" s="4">
         <v>51.677101612091001</v>
       </c>
-      <c r="J186" s="5" t="s">
+      <c r="J186" s="4" t="s">
         <v>682</v>
       </c>
-      <c r="K186" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L186" s="5">
+      <c r="K186" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L186" s="4">
         <v>4.9470424652099602E-2</v>
       </c>
     </row>
@@ -15314,40 +15295,40 @@
       </c>
     </row>
     <row r="188" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A188" s="5" t="s">
+      <c r="A188" s="4" t="s">
         <v>192</v>
       </c>
-      <c r="B188" s="5" t="s">
+      <c r="B188" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C188" s="5">
+      <c r="C188" s="4">
         <v>0.277233124</v>
       </c>
-      <c r="D188" s="5" t="s">
+      <c r="D188" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="E188" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F188" s="5">
+      <c r="E188" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F188" s="4">
         <v>4.3261528015136698E-2</v>
       </c>
-      <c r="G188" s="5" t="s">
+      <c r="G188" s="4" t="s">
         <v>433</v>
       </c>
-      <c r="H188" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I188" s="5">
+      <c r="H188" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I188" s="4">
         <v>52.050680875778198</v>
       </c>
-      <c r="J188" s="5" t="s">
+      <c r="J188" s="4" t="s">
         <v>684</v>
       </c>
-      <c r="K188" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L188" s="5">
+      <c r="K188" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L188" s="4">
         <v>4.4168949127197203E-2</v>
       </c>
     </row>
@@ -15390,40 +15371,40 @@
       </c>
     </row>
     <row r="190" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A190" s="5" t="s">
+      <c r="A190" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="B190" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C190" s="5">
+      <c r="B190" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C190" s="4">
         <v>51.551771879999997</v>
       </c>
-      <c r="D190" s="5" t="s">
+      <c r="D190" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="E190" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F190" s="5">
+      <c r="E190" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F190" s="4">
         <v>0.90518116950988703</v>
       </c>
-      <c r="G190" s="5" t="s">
+      <c r="G190" s="4" t="s">
         <v>435</v>
       </c>
-      <c r="H190" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I190" s="5">
+      <c r="H190" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I190" s="4">
         <v>52.076081514358499</v>
       </c>
-      <c r="J190" s="5" t="s">
+      <c r="J190" s="4" t="s">
         <v>686</v>
       </c>
-      <c r="K190" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L190" s="5">
+      <c r="K190" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L190" s="4">
         <v>0.94353795051574696</v>
       </c>
     </row>
@@ -15466,40 +15447,40 @@
       </c>
     </row>
     <row r="192" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A192" s="5" t="s">
+      <c r="A192" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="B192" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C192" s="5">
+      <c r="B192" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C192" s="4">
         <v>50.795502900000002</v>
       </c>
-      <c r="D192" s="5" t="s">
+      <c r="D192" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="E192" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F192" s="5">
+      <c r="E192" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F192" s="4">
         <v>84.405990839004502</v>
       </c>
-      <c r="G192" s="5" t="s">
+      <c r="G192" s="4" t="s">
         <v>437</v>
       </c>
-      <c r="H192" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I192" s="5">
+      <c r="H192" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I192" s="4">
         <v>51.174524307250898</v>
       </c>
-      <c r="J192" s="5" t="s">
+      <c r="J192" s="4" t="s">
         <v>688</v>
       </c>
-      <c r="K192" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L192" s="5">
+      <c r="K192" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L192" s="4">
         <v>75.052291631698594</v>
       </c>
     </row>
@@ -15542,40 +15523,40 @@
       </c>
     </row>
     <row r="194" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A194" s="5" t="s">
+      <c r="A194" s="4" t="s">
         <v>198</v>
       </c>
-      <c r="B194" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C194" s="5">
+      <c r="B194" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C194" s="4">
         <v>51.648992059999998</v>
       </c>
-      <c r="D194" s="5" t="s">
+      <c r="D194" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="E194" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F194" s="5">
+      <c r="E194" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F194" s="4">
         <v>2.6566505432128899E-2</v>
       </c>
-      <c r="G194" s="5" t="s">
+      <c r="G194" s="4" t="s">
         <v>439</v>
       </c>
-      <c r="H194" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I194" s="5">
+      <c r="H194" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I194" s="4">
         <v>0.13992428779602001</v>
       </c>
-      <c r="J194" s="5" t="s">
+      <c r="J194" s="4" t="s">
         <v>690</v>
       </c>
-      <c r="K194" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L194" s="5">
+      <c r="K194" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L194" s="4">
         <v>68.347760438918996</v>
       </c>
     </row>
@@ -15618,40 +15599,40 @@
       </c>
     </row>
     <row r="196" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A196" s="5" t="s">
+      <c r="A196" s="4" t="s">
         <v>200</v>
       </c>
-      <c r="B196" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C196" s="5">
+      <c r="B196" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C196" s="4">
         <v>51.583440070000002</v>
       </c>
-      <c r="D196" s="5" t="s">
+      <c r="D196" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="E196" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F196" s="5">
+      <c r="E196" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F196" s="4">
         <v>0.87980437278747503</v>
       </c>
-      <c r="G196" s="5" t="s">
+      <c r="G196" s="4" t="s">
         <v>441</v>
       </c>
-      <c r="H196" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I196" s="5">
+      <c r="H196" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I196" s="4">
         <v>51.705372571945098</v>
       </c>
-      <c r="J196" s="5" t="s">
+      <c r="J196" s="4" t="s">
         <v>692</v>
       </c>
-      <c r="K196" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L196" s="5">
+      <c r="K196" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L196" s="4">
         <v>0.90252661705017001</v>
       </c>
     </row>
@@ -15694,40 +15675,40 @@
       </c>
     </row>
     <row r="198" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A198" s="5" t="s">
+      <c r="A198" s="4" t="s">
         <v>202</v>
       </c>
-      <c r="B198" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C198" s="5">
+      <c r="B198" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C198" s="4">
         <v>50.815645930000002</v>
       </c>
-      <c r="D198" s="5" t="s">
+      <c r="D198" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="E198" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F198" s="5">
+      <c r="E198" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F198" s="4">
         <v>0.889304399490356</v>
       </c>
-      <c r="G198" s="5" t="s">
+      <c r="G198" s="4" t="s">
         <v>443</v>
       </c>
-      <c r="H198" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I198" s="5">
+      <c r="H198" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I198" s="4">
         <v>51.421885967254603</v>
       </c>
-      <c r="J198" s="5" t="s">
+      <c r="J198" s="4" t="s">
         <v>694</v>
       </c>
-      <c r="K198" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L198" s="5">
+      <c r="K198" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L198" s="4">
         <v>0.93781471252441395</v>
       </c>
     </row>
@@ -15770,40 +15751,40 @@
       </c>
     </row>
     <row r="200" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A200" s="5" t="s">
+      <c r="A200" s="4" t="s">
         <v>204</v>
       </c>
-      <c r="B200" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C200" s="5">
+      <c r="B200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="C200" s="4">
         <v>1.6722526550000001</v>
       </c>
-      <c r="D200" s="5" t="s">
+      <c r="D200" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="E200" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F200" s="5">
+      <c r="E200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F200" s="4">
         <v>1.6718149185180602E-2</v>
       </c>
-      <c r="G200" s="5" t="s">
+      <c r="G200" s="4" t="s">
         <v>445</v>
       </c>
-      <c r="H200" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I200" s="5">
+      <c r="H200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I200" s="4">
         <v>0.38478851318359297</v>
       </c>
-      <c r="J200" s="5" t="s">
+      <c r="J200" s="4" t="s">
         <v>696</v>
       </c>
-      <c r="K200" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L200" s="5">
+      <c r="K200" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L200" s="4">
         <v>6.2186214923858598</v>
       </c>
     </row>
@@ -15846,40 +15827,40 @@
       </c>
     </row>
     <row r="202" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A202" s="5" t="s">
+      <c r="A202" s="4" t="s">
         <v>206</v>
       </c>
-      <c r="B202" s="5" t="s">
+      <c r="B202" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C202" s="5">
+      <c r="C202" s="4">
         <v>0.17992949499999999</v>
       </c>
-      <c r="D202" s="5" t="s">
+      <c r="D202" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="E202" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F202" s="5">
+      <c r="E202" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F202" s="4">
         <v>6.8440437316894497E-3</v>
       </c>
-      <c r="G202" s="5" t="s">
+      <c r="G202" s="4" t="s">
         <v>447</v>
       </c>
-      <c r="H202" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I202" s="5">
+      <c r="H202" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I202" s="4">
         <v>4.3723583221435504E-3</v>
       </c>
-      <c r="J202" s="5" t="s">
+      <c r="J202" s="4" t="s">
         <v>698</v>
       </c>
-      <c r="K202" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L202" s="5">
+      <c r="K202" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L202" s="4">
         <v>2.6164293289184501E-2</v>
       </c>
     </row>
@@ -15922,40 +15903,40 @@
       </c>
     </row>
     <row r="204" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A204" s="5" t="s">
+      <c r="A204" s="4" t="s">
         <v>208</v>
       </c>
-      <c r="B204" s="5" t="s">
+      <c r="B204" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C204" s="5">
+      <c r="C204" s="4">
         <v>1.1407458779999999</v>
       </c>
-      <c r="D204" s="5" t="s">
+      <c r="D204" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="E204" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F204" s="5">
+      <c r="E204" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F204" s="4">
         <v>8.8862419128417899E-2</v>
       </c>
-      <c r="G204" s="5" t="s">
+      <c r="G204" s="4" t="s">
         <v>449</v>
       </c>
-      <c r="H204" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I204" s="5">
+      <c r="H204" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I204" s="4">
         <v>51.6431756019592</v>
       </c>
-      <c r="J204" s="5" t="s">
+      <c r="J204" s="4" t="s">
         <v>700</v>
       </c>
-      <c r="K204" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L204" s="5">
+      <c r="K204" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L204" s="4">
         <v>0.10751390457153299</v>
       </c>
     </row>
@@ -15998,40 +15979,40 @@
       </c>
     </row>
     <row r="206" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A206" s="5" t="s">
+      <c r="A206" s="4" t="s">
         <v>210</v>
       </c>
-      <c r="B206" s="5" t="s">
+      <c r="B206" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C206" s="5">
+      <c r="C206" s="4">
         <v>0.26555395100000001</v>
       </c>
-      <c r="D206" s="5" t="s">
+      <c r="D206" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="E206" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F206" s="5">
+      <c r="E206" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F206" s="4">
         <v>4.39038276672363E-2</v>
       </c>
-      <c r="G206" s="5" t="s">
+      <c r="G206" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="H206" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I206" s="5">
+      <c r="H206" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I206" s="4">
         <v>51.674841403961103</v>
       </c>
-      <c r="J206" s="5" t="s">
+      <c r="J206" s="4" t="s">
         <v>702</v>
       </c>
-      <c r="K206" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L206" s="5">
+      <c r="K206" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L206" s="4">
         <v>6.2417745590209898E-2</v>
       </c>
     </row>
@@ -16074,40 +16055,40 @@
       </c>
     </row>
     <row r="208" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A208" s="5" t="s">
+      <c r="A208" s="4" t="s">
         <v>212</v>
       </c>
-      <c r="B208" s="5" t="s">
+      <c r="B208" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C208" s="5">
+      <c r="C208" s="4">
         <v>1.1443922520000001</v>
       </c>
-      <c r="D208" s="5" t="s">
+      <c r="D208" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="E208" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F208" s="5">
+      <c r="E208" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F208" s="4">
         <v>8.6674690246582003E-2</v>
       </c>
-      <c r="G208" s="5" t="s">
+      <c r="G208" s="4" t="s">
         <v>453</v>
       </c>
-      <c r="H208" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I208" s="5">
+      <c r="H208" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I208" s="4">
         <v>51.4966106414794</v>
       </c>
-      <c r="J208" s="5" t="s">
+      <c r="J208" s="4" t="s">
         <v>704</v>
       </c>
-      <c r="K208" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L208" s="5">
+      <c r="K208" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L208" s="4">
         <v>8.9462518692016602E-2</v>
       </c>
     </row>
@@ -16150,40 +16131,40 @@
       </c>
     </row>
     <row r="210" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A210" s="5" t="s">
+      <c r="A210" s="4" t="s">
         <v>214</v>
       </c>
-      <c r="B210" s="5" t="s">
+      <c r="B210" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C210" s="5">
+      <c r="C210" s="4">
         <v>5.6880168910000002</v>
       </c>
-      <c r="D210" s="5" t="s">
+      <c r="D210" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="E210" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F210" s="5">
+      <c r="E210" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F210" s="4">
         <v>0.898015737533569</v>
       </c>
-      <c r="G210" s="5" t="s">
+      <c r="G210" s="4" t="s">
         <v>455</v>
       </c>
-      <c r="H210" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I210" s="5">
+      <c r="H210" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I210" s="4">
         <v>51.495101451873701</v>
       </c>
-      <c r="J210" s="5" t="s">
+      <c r="J210" s="4" t="s">
         <v>706</v>
       </c>
-      <c r="K210" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L210" s="5">
+      <c r="K210" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L210" s="4">
         <v>0.96495699882507302</v>
       </c>
     </row>
@@ -16226,40 +16207,40 @@
       </c>
     </row>
     <row r="212" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A212" s="5" t="s">
+      <c r="A212" s="4" t="s">
         <v>216</v>
       </c>
-      <c r="B212" s="5" t="s">
+      <c r="B212" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C212" s="5">
+      <c r="C212" s="4">
         <v>0.203582287</v>
       </c>
-      <c r="D212" s="5" t="s">
+      <c r="D212" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="E212" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F212" s="5">
+      <c r="E212" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F212" s="4">
         <v>9.1929435729980399E-3</v>
       </c>
-      <c r="G212" s="5" t="s">
+      <c r="G212" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="H212" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="I212" s="5">
+      <c r="H212" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="I212" s="4">
         <v>6.0954093933105399E-3</v>
       </c>
-      <c r="J212" s="5" t="s">
+      <c r="J212" s="4" t="s">
         <v>708</v>
       </c>
-      <c r="K212" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L212" s="5">
+      <c r="K212" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L212" s="4">
         <v>9.6092224121093698E-3</v>
       </c>
     </row>
@@ -16302,40 +16283,40 @@
       </c>
     </row>
     <row r="214" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A214" s="5" t="s">
+      <c r="A214" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="B214" s="5" t="s">
+      <c r="B214" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C214" s="5">
+      <c r="C214" s="4">
         <v>0.54297900200000004</v>
       </c>
-      <c r="D214" s="5" t="s">
+      <c r="D214" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="E214" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F214" s="5">
+      <c r="E214" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F214" s="4">
         <v>9.5530748367309501E-2</v>
       </c>
-      <c r="G214" s="5" t="s">
+      <c r="G214" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="H214" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I214" s="5">
+      <c r="H214" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I214" s="4">
         <v>51.547631025314303</v>
       </c>
-      <c r="J214" s="5" t="s">
+      <c r="J214" s="4" t="s">
         <v>710</v>
       </c>
-      <c r="K214" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L214" s="5">
+      <c r="K214" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L214" s="4">
         <v>0.111603498458862</v>
       </c>
     </row>
@@ -16378,40 +16359,40 @@
       </c>
     </row>
     <row r="216" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A216" s="5" t="s">
+      <c r="A216" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="B216" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C216" s="5">
+      <c r="B216" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C216" s="4">
         <v>51.257506849999999</v>
       </c>
-      <c r="D216" s="5" t="s">
+      <c r="D216" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="E216" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F216" s="5">
+      <c r="E216" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F216" s="4">
         <v>0.86323118209838801</v>
       </c>
-      <c r="G216" s="5" t="s">
+      <c r="G216" s="4" t="s">
         <v>461</v>
       </c>
-      <c r="H216" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I216" s="5">
+      <c r="H216" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I216" s="4">
         <v>51.748237371444702</v>
       </c>
-      <c r="J216" s="5" t="s">
+      <c r="J216" s="4" t="s">
         <v>712</v>
       </c>
-      <c r="K216" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L216" s="5">
+      <c r="K216" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L216" s="4">
         <v>0.90252375602722101</v>
       </c>
     </row>
@@ -16454,40 +16435,40 @@
       </c>
     </row>
     <row r="218" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A218" s="5" t="s">
+      <c r="A218" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="B218" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C218" s="5">
+      <c r="B218" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C218" s="4">
         <v>50.5734396</v>
       </c>
-      <c r="D218" s="5" t="s">
+      <c r="D218" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="E218" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F218" s="5">
+      <c r="E218" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F218" s="4">
         <v>76.162044763565007</v>
       </c>
-      <c r="G218" s="5" t="s">
+      <c r="G218" s="4" t="s">
         <v>463</v>
       </c>
-      <c r="H218" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I218" s="5">
+      <c r="H218" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I218" s="4">
         <v>52.740134000778198</v>
       </c>
-      <c r="J218" s="5" t="s">
+      <c r="J218" s="4" t="s">
         <v>714</v>
       </c>
-      <c r="K218" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L218" s="5">
+      <c r="K218" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L218" s="4">
         <v>74.551083326339693</v>
       </c>
     </row>
@@ -16530,40 +16511,40 @@
       </c>
     </row>
     <row r="220" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A220" s="5" t="s">
+      <c r="A220" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="B220" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C220" s="5">
+      <c r="B220" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C220" s="4">
         <v>50.665179729999998</v>
       </c>
-      <c r="D220" s="5" t="s">
+      <c r="D220" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="E220" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F220" s="5">
+      <c r="E220" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F220" s="4">
         <v>139.56286859512301</v>
       </c>
-      <c r="G220" s="5" t="s">
+      <c r="G220" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="H220" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I220" s="5">
+      <c r="H220" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I220" s="4">
         <v>51.400379896163898</v>
       </c>
-      <c r="J220" s="5" t="s">
+      <c r="J220" s="4" t="s">
         <v>716</v>
       </c>
-      <c r="K220" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L220" s="5">
+      <c r="K220" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L220" s="4">
         <v>128.67160749435399</v>
       </c>
     </row>
@@ -16606,40 +16587,40 @@
       </c>
     </row>
     <row r="222" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A222" s="5" t="s">
+      <c r="A222" s="4" t="s">
         <v>226</v>
       </c>
-      <c r="B222" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C222" s="5">
+      <c r="B222" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C222" s="4">
         <v>50.710975650000002</v>
       </c>
-      <c r="D222" s="5" t="s">
+      <c r="D222" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="E222" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F222" s="5">
+      <c r="E222" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F222" s="4">
         <v>2.6376485824584898E-2</v>
       </c>
-      <c r="G222" s="5" t="s">
+      <c r="G222" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="H222" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I222" s="5">
+      <c r="H222" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I222" s="4">
         <v>0.85054850578308105</v>
       </c>
-      <c r="J222" s="5" t="s">
+      <c r="J222" s="4" t="s">
         <v>718</v>
       </c>
-      <c r="K222" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L222" s="5">
+      <c r="K222" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L222" s="4">
         <v>134.13078141212401</v>
       </c>
     </row>
@@ -16682,40 +16663,40 @@
       </c>
     </row>
     <row r="224" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A224" s="5" t="s">
+      <c r="A224" s="4" t="s">
         <v>228</v>
       </c>
-      <c r="B224" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C224" s="5">
+      <c r="B224" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C224" s="4">
         <v>50.040786269999998</v>
       </c>
-      <c r="D224" s="5" t="s">
+      <c r="D224" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="E224" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F224" s="5">
+      <c r="E224" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F224" s="4">
         <v>2.50880718231201E-2</v>
       </c>
-      <c r="G224" s="5" t="s">
+      <c r="G224" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="H224" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I224" s="5">
+      <c r="H224" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I224" s="4">
         <v>1.5756101608276301</v>
       </c>
-      <c r="J224" s="5" t="s">
+      <c r="J224" s="4" t="s">
         <v>720</v>
       </c>
-      <c r="K224" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L224" s="5">
+      <c r="K224" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L224" s="4">
         <v>286.88010406494101</v>
       </c>
     </row>
@@ -16758,40 +16739,40 @@
       </c>
     </row>
     <row r="226" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A226" s="5" t="s">
+      <c r="A226" s="4" t="s">
         <v>230</v>
       </c>
-      <c r="B226" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C226" s="5">
+      <c r="B226" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C226" s="4">
         <v>50.55034208</v>
       </c>
-      <c r="D226" s="5" t="s">
+      <c r="D226" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="E226" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F226" s="5">
+      <c r="E226" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F226" s="4">
         <v>3.7870168685913003E-2</v>
       </c>
-      <c r="G226" s="5" t="s">
+      <c r="G226" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="H226" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I226" s="5">
+      <c r="H226" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="I226" s="4">
         <v>1.58113360404968</v>
       </c>
-      <c r="J226" s="5" t="s">
+      <c r="J226" s="4" t="s">
         <v>722</v>
       </c>
-      <c r="K226" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L226" s="5">
+      <c r="K226" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L226" s="4">
         <v>303.60427546501103</v>
       </c>
     </row>
@@ -16834,40 +16815,40 @@
       </c>
     </row>
     <row r="228" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A228" s="5" t="s">
+      <c r="A228" s="4" t="s">
         <v>232</v>
       </c>
-      <c r="B228" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C228" s="5">
+      <c r="B228" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C228" s="4">
         <v>51.009992599999997</v>
       </c>
-      <c r="D228" s="5" t="s">
+      <c r="D228" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="E228" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="F228" s="5">
+      <c r="E228" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="F228" s="4">
         <v>224.089176177978</v>
       </c>
-      <c r="G228" s="5" t="s">
+      <c r="G228" s="4" t="s">
         <v>473</v>
       </c>
-      <c r="H228" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I228" s="5">
+      <c r="H228" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I228" s="4">
         <v>52.292772531509399</v>
       </c>
-      <c r="J228" s="5" t="s">
+      <c r="J228" s="4" t="s">
         <v>724</v>
       </c>
-      <c r="K228" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="L228" s="5">
+      <c r="K228" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="L228" s="4">
         <v>301.04605245590199</v>
       </c>
     </row>
@@ -16910,40 +16891,40 @@
       </c>
     </row>
     <row r="230" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A230" s="5" t="s">
+      <c r="A230" s="4" t="s">
         <v>234</v>
       </c>
-      <c r="B230" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C230" s="5">
+      <c r="B230" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C230" s="4">
         <v>51.132117030000003</v>
       </c>
-      <c r="D230" s="5" t="s">
+      <c r="D230" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="E230" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F230" s="5">
+      <c r="E230" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F230" s="4">
         <v>0.87545013427734297</v>
       </c>
-      <c r="G230" s="5" t="s">
+      <c r="G230" s="4" t="s">
         <v>475</v>
       </c>
-      <c r="H230" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I230" s="5">
+      <c r="H230" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I230" s="4">
         <v>52.406781196594203</v>
       </c>
-      <c r="J230" s="5" t="s">
+      <c r="J230" s="4" t="s">
         <v>726</v>
       </c>
-      <c r="K230" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L230" s="5">
+      <c r="K230" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L230" s="4">
         <v>0.88439631462097101</v>
       </c>
     </row>
@@ -16986,40 +16967,40 @@
       </c>
     </row>
     <row r="232" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A232" s="5" t="s">
+      <c r="A232" s="4" t="s">
         <v>236</v>
       </c>
-      <c r="B232" s="5" t="s">
+      <c r="B232" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C232" s="5">
+      <c r="C232" s="4">
         <v>1.1524167059999999</v>
       </c>
-      <c r="D232" s="5" t="s">
+      <c r="D232" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="E232" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F232" s="5">
+      <c r="E232" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F232" s="4">
         <v>8.6757183074951102E-2</v>
       </c>
-      <c r="G232" s="5" t="s">
+      <c r="G232" s="4" t="s">
         <v>477</v>
       </c>
-      <c r="H232" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I232" s="5">
+      <c r="H232" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I232" s="4">
         <v>51.053930759429903</v>
       </c>
-      <c r="J232" s="5" t="s">
+      <c r="J232" s="4" t="s">
         <v>728</v>
       </c>
-      <c r="K232" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L232" s="5">
+      <c r="K232" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L232" s="4">
         <v>9.8330020904541002E-2</v>
       </c>
     </row>
@@ -17062,40 +17043,40 @@
       </c>
     </row>
     <row r="234" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A234" s="5" t="s">
+      <c r="A234" s="4" t="s">
         <v>238</v>
       </c>
-      <c r="B234" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C234" s="5">
+      <c r="B234" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C234" s="4">
         <v>51.241774560000003</v>
       </c>
-      <c r="D234" s="5" t="s">
+      <c r="D234" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="E234" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F234" s="5">
+      <c r="E234" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F234" s="4">
         <v>0.57296991348266602</v>
       </c>
-      <c r="G234" s="5" t="s">
+      <c r="G234" s="4" t="s">
         <v>479</v>
       </c>
-      <c r="H234" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I234" s="5">
+      <c r="H234" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I234" s="4">
         <v>51.475125312805098</v>
       </c>
-      <c r="J234" s="5" t="s">
+      <c r="J234" s="4" t="s">
         <v>730</v>
       </c>
-      <c r="K234" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L234" s="5">
+      <c r="K234" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L234" s="4">
         <v>0.56188797950744596</v>
       </c>
     </row>
@@ -17138,40 +17119,40 @@
       </c>
     </row>
     <row r="236" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A236" s="5" t="s">
+      <c r="A236" s="4" t="s">
         <v>240</v>
       </c>
-      <c r="B236" s="5" t="s">
+      <c r="B236" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C236" s="5">
+      <c r="C236" s="4">
         <v>0.48702669100000001</v>
       </c>
-      <c r="D236" s="5" t="s">
+      <c r="D236" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="E236" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F236" s="5">
+      <c r="E236" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F236" s="4">
         <v>8.08432102203369E-2</v>
       </c>
-      <c r="G236" s="5" t="s">
+      <c r="G236" s="4" t="s">
         <v>481</v>
       </c>
-      <c r="H236" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I236" s="5">
+      <c r="H236" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I236" s="4">
         <v>51.370226621627801</v>
       </c>
-      <c r="J236" s="5" t="s">
+      <c r="J236" s="4" t="s">
         <v>732</v>
       </c>
-      <c r="K236" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L236" s="5">
+      <c r="K236" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L236" s="4">
         <v>0.113521337509155</v>
       </c>
     </row>
@@ -17214,40 +17195,40 @@
       </c>
     </row>
     <row r="238" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A238" s="5" t="s">
+      <c r="A238" s="4" t="s">
         <v>242</v>
       </c>
-      <c r="B238" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C238" s="5">
+      <c r="B238" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="C238" s="4">
         <v>50.626649380000003</v>
       </c>
-      <c r="D238" s="5" t="s">
+      <c r="D238" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="E238" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="F238" s="5">
+      <c r="E238" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F238" s="4">
         <v>0.53390550613403298</v>
       </c>
-      <c r="G238" s="5" t="s">
+      <c r="G238" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="H238" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I238" s="5">
+      <c r="H238" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I238" s="4">
         <v>51.692182540893498</v>
       </c>
-      <c r="J238" s="5" t="s">
+      <c r="J238" s="4" t="s">
         <v>734</v>
       </c>
-      <c r="K238" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="L238" s="5">
+      <c r="K238" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="L238" s="4">
         <v>0.59201741218566895</v>
       </c>
     </row>
@@ -17290,40 +17271,40 @@
       </c>
     </row>
     <row r="240" spans="1:12" x14ac:dyDescent="0.35">
-      <c r="A240" s="5" t="s">
+      <c r="A240" s="4" t="s">
         <v>244</v>
       </c>
-      <c r="B240" s="5" t="s">
+      <c r="B240" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="C240" s="5">
+      <c r="C240" s="4">
         <v>25.792720790000001</v>
       </c>
-      <c r="D240" s="5" t="s">
+      <c r="D240" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="E240" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="F240" s="5">
+      <c r="E240" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="F240" s="4">
         <v>0.84482264518737704</v>
       </c>
-      <c r="G240" s="5" t="s">
+      <c r="G240" s="4" t="s">
         <v>485</v>
       </c>
-      <c r="H240" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="I240" s="5">
+      <c r="H240" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="I240" s="4">
         <v>51.548269748687702</v>
       </c>
-      <c r="J240" s="5" t="s">
+      <c r="J240" s="4" t="s">
         <v>736</v>
       </c>
-      <c r="K240" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L240" s="5">
+      <c r="K240" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="L240" s="4">
         <v>0.84664416313171298</v>
       </c>
     </row>
